--- a/epsilon-phi-core/src/python/epsilonPhi/ep_saa/marketing/Marketing Charts.xlsx
+++ b/epsilon-phi-core/src/python/epsilonPhi/ep_saa/marketing/Marketing Charts.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/francisbarker/repo/epsilon-psi/epsilon-phi-core/src/python/epsilonPhi/ep_saa/marketing/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/francisbarker/Repositories/Python/epsilon-phi/epsilon-phi-core/src/python/epsilonPhi/ep_saa/marketing/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{004BCA16-4356-5846-8F24-CE91C7C7E0DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6F47CBA-CA86-D94D-945F-D5C203EC678A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3480" yWindow="500" windowWidth="28040" windowHeight="17440" activeTab="2" xr2:uid="{B5A52BBA-49B5-954D-A188-236E4982FCC2}"/>
+    <workbookView xWindow="11140" yWindow="8680" windowWidth="37520" windowHeight="17440" activeTab="1" xr2:uid="{B5A52BBA-49B5-954D-A188-236E4982FCC2}"/>
   </bookViews>
   <sheets>
     <sheet name="Risk Premia Charts" sheetId="1" r:id="rId1"/>
@@ -379,7 +379,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -421,12 +421,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="9" fontId="6" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -503,6 +497,24 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -512,6 +524,8 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FF2CBAF0"/>
+      <color rgb="FF994010"/>
       <color rgb="FFF2F2F2"/>
       <color rgb="FFDAE9F8"/>
       <color rgb="FFA6C9EC"/>
@@ -1438,9 +1452,9 @@
             <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
-                <a:schemeClr val="accent2">
-                  <a:lumMod val="60000"/>
-                </a:schemeClr>
+                <a:srgbClr val="994010">
+                  <a:alpha val="76078"/>
+                </a:srgbClr>
               </a:solidFill>
               <a:ln w="19050">
                 <a:solidFill>
@@ -1527,10 +1541,9 @@
             <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
-                <a:schemeClr val="accent4">
-                  <a:lumMod val="80000"/>
-                  <a:lumOff val="20000"/>
-                </a:schemeClr>
+                <a:srgbClr val="2CBAF0">
+                  <a:alpha val="75294"/>
+                </a:srgbClr>
               </a:solidFill>
               <a:ln w="19050">
                 <a:solidFill>
@@ -2430,7 +2443,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v>0.1</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>0</c:v>
@@ -2442,7 +2455,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0</c:v>
+                  <c:v>0.35</c:v>
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>0</c:v>
@@ -2451,7 +2464,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0</c:v>
+                  <c:v>0.2</c:v>
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>0</c:v>
@@ -2460,22 +2473,22 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="15">
                   <c:v>0.25</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.35</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.2</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0</c:v>
+                  <c:v>0.1</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2580,13 +2593,12 @@
             <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
+                <a:schemeClr val="accent2"/>
               </a:solidFill>
               <a:ln w="19050">
-                <a:noFill/>
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
               </a:ln>
               <a:effectLst/>
             </c:spPr>
@@ -3037,7 +3049,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v>0.1</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>0</c:v>
@@ -3049,7 +3061,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0</c:v>
+                  <c:v>0.35</c:v>
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>0</c:v>
@@ -3058,7 +3070,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0</c:v>
+                  <c:v>0.2</c:v>
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>0</c:v>
@@ -3067,22 +3079,22 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="15">
                   <c:v>0.25</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.35</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.2</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0</c:v>
+                  <c:v>0.1</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3330,6 +3342,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000B-3681-8348-8EBA-9A3F091838EA}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:val>
             <c:numRef>
@@ -8222,7 +8239,7 @@
         <v>4.887311420827025E-2</v>
       </c>
       <c r="E8" s="7">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="F8" s="2"/>
       <c r="G8" s="2"/>
@@ -8330,7 +8347,7 @@
         <v>2.5141806970496217E-2</v>
       </c>
       <c r="E12" s="7">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="F12" s="2"/>
       <c r="G12" s="2"/>
@@ -8411,7 +8428,7 @@
         <v>4.1350417532572348E-2</v>
       </c>
       <c r="E15" s="7">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="F15" s="2"/>
       <c r="G15" s="2"/>
@@ -8489,7 +8506,7 @@
         <v>8.0480839231394499E-2</v>
       </c>
       <c r="E18" s="7">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="F18" s="2"/>
       <c r="G18" s="2"/>
@@ -8537,7 +8554,7 @@
         <v>8.5158690353384581E-2</v>
       </c>
       <c r="E20" s="7">
-        <v>0.35</v>
+        <v>0</v>
       </c>
       <c r="F20" s="2"/>
       <c r="G20" s="2"/>
@@ -8561,7 +8578,7 @@
         <v>4.3290129194193519E-2</v>
       </c>
       <c r="E21" s="7">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="F21" s="2"/>
       <c r="G21" s="2"/>
@@ -8585,7 +8602,7 @@
         <v>8.0409289218157612E-2</v>
       </c>
       <c r="E22" s="7">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="F22" s="2"/>
       <c r="G22" s="2"/>
@@ -8609,7 +8626,7 @@
         <v>2.1040329438565958E-2</v>
       </c>
       <c r="E23" s="7">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="F23" s="2"/>
       <c r="G23" s="2"/>
@@ -8843,8 +8860,8 @@
     </row>
     <row r="4" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2"/>
-      <c r="B4" s="36"/>
-      <c r="C4" s="37" t="s">
+      <c r="B4" s="34"/>
+      <c r="C4" s="35" t="s">
         <v>16</v>
       </c>
       <c r="D4" s="2"/>
@@ -8862,10 +8879,10 @@
     </row>
     <row r="5" spans="1:15" s="12" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="10"/>
-      <c r="B5" s="38" t="s">
+      <c r="B5" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="C5" s="35" t="s">
+      <c r="C5" s="33" t="s">
         <v>11</v>
       </c>
       <c r="D5" s="11"/>
@@ -8883,10 +8900,10 @@
     </row>
     <row r="6" spans="1:15" s="12" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="10"/>
-      <c r="B6" s="39" t="s">
+      <c r="B6" s="37" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="35" t="s">
+      <c r="C6" s="33" t="s">
         <v>10</v>
       </c>
       <c r="D6" s="11"/>
@@ -8904,10 +8921,10 @@
     </row>
     <row r="7" spans="1:15" s="12" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="10"/>
-      <c r="B7" s="40" t="s">
+      <c r="B7" s="38" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="35" t="s">
+      <c r="C7" s="33" t="s">
         <v>12</v>
       </c>
       <c r="D7" s="11"/>
@@ -8925,10 +8942,10 @@
     </row>
     <row r="8" spans="1:15" s="12" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="10"/>
-      <c r="B8" s="41" t="s">
+      <c r="B8" s="39" t="s">
         <v>3</v>
       </c>
-      <c r="C8" s="35" t="s">
+      <c r="C8" s="33" t="s">
         <v>13</v>
       </c>
       <c r="D8" s="11"/>
@@ -8946,10 +8963,10 @@
     </row>
     <row r="9" spans="1:15" s="12" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="10"/>
-      <c r="B9" s="42" t="s">
+      <c r="B9" s="40" t="s">
         <v>4</v>
       </c>
-      <c r="C9" s="35" t="s">
+      <c r="C9" s="33" t="s">
         <v>14</v>
       </c>
       <c r="D9" s="11"/>
@@ -8967,10 +8984,10 @@
     </row>
     <row r="10" spans="1:15" s="12" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="10"/>
-      <c r="B10" s="43" t="s">
+      <c r="B10" s="41" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="44" t="s">
+      <c r="C10" s="42" t="s">
         <v>15</v>
       </c>
       <c r="D10" s="11"/>
@@ -9268,14 +9285,14 @@
   <dimension ref="A1:K389"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="3" max="3" width="9.83203125" style="29" customWidth="1"/>
+    <col min="3" max="3" width="9.83203125" style="27" customWidth="1"/>
     <col min="4" max="7" width="9.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
-      <c r="C1" s="27"/>
+      <c r="C1" s="25"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
@@ -9288,7 +9305,7 @@
     <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
-      <c r="C2" s="27"/>
+      <c r="C2" s="25"/>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
@@ -9301,13 +9318,13 @@
     <row r="3" spans="1:11" s="12" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="10"/>
       <c r="B3" s="10"/>
-      <c r="C3" s="28"/>
-      <c r="D3" s="16" t="s">
+      <c r="C3" s="26"/>
+      <c r="D3" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="E3" s="16"/>
-      <c r="F3" s="16"/>
-      <c r="G3" s="16"/>
+      <c r="E3" s="44"/>
+      <c r="F3" s="44"/>
+      <c r="G3" s="45"/>
       <c r="H3" s="10"/>
       <c r="I3" s="10"/>
       <c r="J3" s="10"/>
@@ -9316,17 +9333,17 @@
     <row r="4" spans="1:11" s="12" customFormat="1" ht="29" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="10"/>
       <c r="B4" s="10"/>
-      <c r="C4" s="28"/>
-      <c r="D4" s="17" t="s">
+      <c r="C4" s="26"/>
+      <c r="D4" s="46" t="s">
         <v>18</v>
       </c>
-      <c r="E4" s="17" t="s">
+      <c r="E4" s="47" t="s">
         <v>19</v>
       </c>
-      <c r="F4" s="17" t="s">
+      <c r="F4" s="47" t="s">
         <v>20</v>
       </c>
-      <c r="G4" s="17" t="s">
+      <c r="G4" s="48" t="s">
         <v>21</v>
       </c>
       <c r="H4" s="10"/>
@@ -9337,18 +9354,18 @@
     <row r="5" spans="1:11" s="12" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="10"/>
       <c r="B5" s="10"/>
-      <c r="C5" s="28"/>
-      <c r="D5" s="18">
+      <c r="C5" s="26"/>
+      <c r="D5" s="16">
         <v>0.9</v>
       </c>
-      <c r="E5" s="21">
+      <c r="E5" s="19">
         <f>-1*E12</f>
         <v>8.7472178090044067E-3</v>
       </c>
-      <c r="F5" s="21">
+      <c r="F5" s="19">
         <v>6.4000000000000001E-2</v>
       </c>
-      <c r="G5" s="21">
+      <c r="G5" s="19">
         <f>-1*D24</f>
         <v>6.1803666624076527E-2</v>
       </c>
@@ -9360,18 +9377,18 @@
     <row r="6" spans="1:11" s="12" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="10"/>
       <c r="B6" s="10"/>
-      <c r="C6" s="28"/>
-      <c r="D6" s="19">
+      <c r="C6" s="26"/>
+      <c r="D6" s="17">
         <v>0.95</v>
       </c>
-      <c r="E6" s="22">
+      <c r="E6" s="20">
         <f>-1*D12</f>
         <v>3.2145193130419913E-2</v>
       </c>
-      <c r="F6" s="22">
+      <c r="F6" s="20">
         <v>9.4E-2</v>
       </c>
-      <c r="G6" s="22">
+      <c r="G6" s="20">
         <f>-1*D23</f>
         <v>9.0484010587685001E-2</v>
       </c>
@@ -9383,18 +9400,18 @@
     <row r="7" spans="1:11" s="12" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="10"/>
       <c r="B7" s="10"/>
-      <c r="C7" s="28"/>
-      <c r="D7" s="20">
+      <c r="C7" s="26"/>
+      <c r="D7" s="18">
         <v>0.99</v>
       </c>
-      <c r="E7" s="23">
+      <c r="E7" s="21">
         <f>-1*C12</f>
         <v>7.6035903558362594E-2</v>
       </c>
-      <c r="F7" s="23">
+      <c r="F7" s="21">
         <v>0.17100000000000001</v>
       </c>
-      <c r="G7" s="23">
+      <c r="G7" s="21">
         <f>-1*D22</f>
         <v>0.15093811269184926</v>
       </c>
@@ -9406,7 +9423,7 @@
     <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
-      <c r="C8" s="27"/>
+      <c r="C8" s="25"/>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
       <c r="F8" s="2"/>
@@ -9419,7 +9436,7 @@
     <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
-      <c r="C9" s="27"/>
+      <c r="C9" s="25"/>
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
@@ -9432,11 +9449,11 @@
     <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
-      <c r="C10" s="27">
+      <c r="C10" s="25">
         <f>AVERAGE(C14:C389)*12</f>
         <v>7.3789368379401865E-2</v>
       </c>
-      <c r="D10" s="26">
+      <c r="D10" s="24">
         <v>7.8299999999999995E-2</v>
       </c>
       <c r="E10" s="2"/>
@@ -9450,7 +9467,7 @@
     <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
-      <c r="C11" s="27">
+      <c r="C11" s="25">
         <f>STDEV(C14:C389)*SQRT(12)</f>
         <v>6.4403640405473667E-2</v>
       </c>
@@ -9470,15 +9487,15 @@
       <c r="B12" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C12" s="27">
+      <c r="C12" s="25">
         <f>$C$10 + _xlfn.NORM.S.INV(0.01)*$C$11</f>
         <v>-7.6035903558362594E-2</v>
       </c>
-      <c r="D12" s="27">
+      <c r="D12" s="25">
         <f>$C$10 + _xlfn.NORM.S.INV(0.05)*$C$11</f>
         <v>-3.2145193130419913E-2</v>
       </c>
-      <c r="E12" s="27">
+      <c r="E12" s="25">
         <f>$C$10 + _xlfn.NORM.S.INV(0.1)*$C$11</f>
         <v>-8.7472178090044067E-3</v>
       </c>
@@ -9490,7 +9507,7 @@
       <c r="K12" s="2"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A13" s="24">
+      <c r="A13" s="22">
         <v>34334</v>
       </c>
       <c r="B13" s="2">
@@ -9507,24 +9524,24 @@
       <c r="K13" s="2"/>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A14" s="24">
+      <c r="A14" s="22">
         <v>34365</v>
       </c>
       <c r="B14" s="2">
         <v>1.0367999999999999</v>
       </c>
-      <c r="C14" s="27">
+      <c r="C14" s="25">
         <f>B14/B13-1</f>
         <v>3.6799999999999944E-2</v>
       </c>
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
       <c r="F14" s="2"/>
-      <c r="G14" s="27">
+      <c r="G14" s="25">
         <f>AVERAGE(C14:C389)</f>
         <v>6.1491140316168227E-3</v>
       </c>
-      <c r="H14" s="26">
+      <c r="H14" s="24">
         <f>$G$14 + _xlfn.NORM.S.INV(0.01)*$G$15</f>
         <v>-3.7101716510721777E-2</v>
       </c>
@@ -9536,24 +9553,24 @@
       <c r="K14" s="2"/>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A15" s="24">
+      <c r="A15" s="22">
         <v>34393</v>
       </c>
       <c r="B15" s="2">
         <v>1.0351999999999999</v>
       </c>
-      <c r="C15" s="27">
+      <c r="C15" s="25">
         <f t="shared" ref="C15:C78" si="0">B15/B14-1</f>
         <v>-1.5432098765432167E-3</v>
       </c>
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
       <c r="F15" s="2"/>
-      <c r="G15" s="27">
+      <c r="G15" s="25">
         <f>STDEV(C14:C389)</f>
         <v>1.8591729562446042E-2</v>
       </c>
-      <c r="H15" s="26">
+      <c r="H15" s="24">
         <f>$G$14 + _xlfn.NORM.S.INV(0.05)*$G$15</f>
         <v>-2.4431559770473468E-2</v>
       </c>
@@ -9565,13 +9582,13 @@
       <c r="K15" s="2"/>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A16" s="24">
+      <c r="A16" s="22">
         <v>34424</v>
       </c>
       <c r="B16" s="2">
         <v>1.0218</v>
       </c>
-      <c r="C16" s="27">
+      <c r="C16" s="25">
         <f t="shared" si="0"/>
         <v>-1.2944358578052428E-2</v>
       </c>
@@ -9579,7 +9596,7 @@
       <c r="E16" s="2"/>
       <c r="F16" s="2"/>
       <c r="G16" s="2"/>
-      <c r="H16" s="26">
+      <c r="H16" s="24">
         <f>$G$14 + _xlfn.NORM.S.INV(0.2)*$G$15</f>
         <v>-9.4980803369830395E-3</v>
       </c>
@@ -9591,13 +9608,13 @@
       <c r="K16" s="2"/>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A17" s="24">
+      <c r="A17" s="22">
         <v>34453</v>
       </c>
       <c r="B17" s="2">
         <v>1.0150999999999999</v>
       </c>
-      <c r="C17" s="27">
+      <c r="C17" s="25">
         <f t="shared" si="0"/>
         <v>-6.5570561753769407E-3</v>
       </c>
@@ -9611,13 +9628,13 @@
       <c r="K17" s="2"/>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A18" s="24">
+      <c r="A18" s="22">
         <v>34485</v>
       </c>
       <c r="B18" s="2">
         <v>1.0136000000000001</v>
       </c>
-      <c r="C18" s="27">
+      <c r="C18" s="25">
         <f t="shared" si="0"/>
         <v>-1.4776869273961379E-3</v>
       </c>
@@ -9631,13 +9648,13 @@
       <c r="K18" s="2"/>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A19" s="24">
+      <c r="A19" s="22">
         <v>34515</v>
       </c>
       <c r="B19" s="2">
         <v>1.0123</v>
       </c>
-      <c r="C19" s="27">
+      <c r="C19" s="25">
         <f t="shared" si="0"/>
         <v>-1.282557221783831E-3</v>
       </c>
@@ -9651,13 +9668,13 @@
       <c r="K19" s="2"/>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A20" s="24">
+      <c r="A20" s="22">
         <v>34544</v>
       </c>
       <c r="B20" s="2">
         <v>1.01779999999999</v>
       </c>
-      <c r="C20" s="27">
+      <c r="C20" s="25">
         <f t="shared" si="0"/>
         <v>5.43317198457971E-3</v>
       </c>
@@ -9671,13 +9688,13 @@
       <c r="K20" s="2"/>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A21" s="24">
+      <c r="A21" s="22">
         <v>34577</v>
       </c>
       <c r="B21" s="2">
         <v>1.02609999999999</v>
       </c>
-      <c r="C21" s="27">
+      <c r="C21" s="25">
         <f t="shared" si="0"/>
         <v>8.1548437807035246E-3</v>
       </c>
@@ -9691,13 +9708,13 @@
       <c r="K21" s="2"/>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A22" s="24">
+      <c r="A22" s="22">
         <v>34607</v>
       </c>
       <c r="B22" s="2">
         <v>1.0337999999999901</v>
       </c>
-      <c r="C22" s="27">
+      <c r="C22" s="25">
         <f t="shared" si="0"/>
         <v>7.5041418965013928E-3</v>
       </c>
@@ -9714,13 +9731,13 @@
       <c r="K22" s="2"/>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A23" s="24">
+      <c r="A23" s="22">
         <v>34638</v>
       </c>
       <c r="B23" s="2">
         <v>1.02629999999999</v>
       </c>
-      <c r="C23" s="27">
+      <c r="C23" s="25">
         <f t="shared" si="0"/>
         <v>-7.2547881601858766E-3</v>
       </c>
@@ -9737,13 +9754,13 @@
       <c r="K23" s="2"/>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A24" s="24">
+      <c r="A24" s="22">
         <v>34668</v>
       </c>
       <c r="B24" s="2">
         <v>1.0153999999999901</v>
       </c>
-      <c r="C24" s="27">
+      <c r="C24" s="25">
         <f t="shared" si="0"/>
         <v>-1.0620676215531533E-2</v>
       </c>
@@ -9760,13 +9777,13 @@
       <c r="K24" s="2"/>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A25" s="24">
+      <c r="A25" s="22">
         <v>34698</v>
       </c>
       <c r="B25" s="2">
         <v>1.0074999999999901</v>
       </c>
-      <c r="C25" s="27">
+      <c r="C25" s="25">
         <f t="shared" si="0"/>
         <v>-7.7801851487099283E-3</v>
       </c>
@@ -9783,13 +9800,13 @@
       <c r="K25" s="2"/>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A26" s="24">
+      <c r="A26" s="22">
         <v>34730</v>
       </c>
       <c r="B26" s="2">
         <v>1.01259999999999</v>
       </c>
-      <c r="C26" s="27">
+      <c r="C26" s="25">
         <f t="shared" si="0"/>
         <v>5.0620347394541021E-3</v>
       </c>
@@ -9806,13 +9823,13 @@
       <c r="K26" s="2"/>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A27" s="24">
+      <c r="A27" s="22">
         <v>34758</v>
       </c>
       <c r="B27" s="2">
         <v>1.0369999999999899</v>
       </c>
-      <c r="C27" s="27">
+      <c r="C27" s="25">
         <f t="shared" si="0"/>
         <v>2.4096385542168974E-2</v>
       </c>
@@ -9829,13 +9846,13 @@
       <c r="K27" s="2"/>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A28" s="24">
+      <c r="A28" s="22">
         <v>34789</v>
       </c>
       <c r="B28" s="2">
         <v>1.0457999999999901</v>
       </c>
-      <c r="C28" s="27">
+      <c r="C28" s="25">
         <f t="shared" si="0"/>
         <v>8.4860173577629983E-3</v>
       </c>
@@ -9852,13 +9869,13 @@
       <c r="K28" s="2"/>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A29" s="25">
+      <c r="A29" s="23">
         <v>34817</v>
       </c>
       <c r="B29">
         <v>1.0677999999999901</v>
       </c>
-      <c r="C29" s="27">
+      <c r="C29" s="25">
         <f t="shared" si="0"/>
         <v>2.1036527060623644E-2</v>
       </c>
@@ -9868,13 +9885,13 @@
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A30" s="25">
+      <c r="A30" s="23">
         <v>34850</v>
       </c>
       <c r="B30">
         <v>1.0798999999999901</v>
       </c>
-      <c r="C30" s="27">
+      <c r="C30" s="25">
         <f t="shared" si="0"/>
         <v>1.1331710058063438E-2</v>
       </c>
@@ -9884,13 +9901,13 @@
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A31" s="25">
+      <c r="A31" s="23">
         <v>34880</v>
       </c>
       <c r="B31">
         <v>1.0938999999999901</v>
       </c>
-      <c r="C31" s="27">
+      <c r="C31" s="25">
         <f t="shared" si="0"/>
         <v>1.2964163348458291E-2</v>
       </c>
@@ -9900,13 +9917,13 @@
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A32" s="25">
+      <c r="A32" s="23">
         <v>34911</v>
       </c>
       <c r="B32">
         <v>1.1184999999999901</v>
       </c>
-      <c r="C32" s="27">
+      <c r="C32" s="25">
         <f t="shared" si="0"/>
         <v>2.2488344455617648E-2</v>
       </c>
@@ -9916,13 +9933,13 @@
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A33" s="25">
+      <c r="A33" s="23">
         <v>34942</v>
       </c>
       <c r="B33">
         <v>1.1356999999999899</v>
       </c>
-      <c r="C33" s="27">
+      <c r="C33" s="25">
         <f t="shared" si="0"/>
         <v>1.5377738042020583E-2</v>
       </c>
@@ -9932,13 +9949,13 @@
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A34" s="25">
+      <c r="A34" s="23">
         <v>34971</v>
       </c>
       <c r="B34">
         <v>1.15689999999999</v>
       </c>
-      <c r="C34" s="27">
+      <c r="C34" s="25">
         <f t="shared" si="0"/>
         <v>1.8666901470459019E-2</v>
       </c>
@@ -9948,13 +9965,13 @@
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A35" s="25">
+      <c r="A35" s="23">
         <v>35003</v>
       </c>
       <c r="B35">
         <v>1.1538999999999999</v>
       </c>
-      <c r="C35" s="27">
+      <c r="C35" s="25">
         <f t="shared" si="0"/>
         <v>-2.5931368311782332E-3</v>
       </c>
@@ -9964,13 +9981,13 @@
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A36" s="25">
+      <c r="A36" s="23">
         <v>35033</v>
       </c>
       <c r="B36">
         <v>1.1668999999999901</v>
       </c>
-      <c r="C36" s="27">
+      <c r="C36" s="25">
         <f t="shared" si="0"/>
         <v>1.1266140913415379E-2</v>
       </c>
@@ -9980,13 +9997,13 @@
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A37" s="25">
+      <c r="A37" s="23">
         <v>35062</v>
       </c>
       <c r="B37">
         <v>1.1922999999999999</v>
       </c>
-      <c r="C37" s="27">
+      <c r="C37" s="25">
         <f t="shared" si="0"/>
         <v>2.1767075156405857E-2</v>
       </c>
@@ -9996,13 +10013,13 @@
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A38" s="25">
+      <c r="A38" s="23">
         <v>35095</v>
       </c>
       <c r="B38">
         <v>1.23389999999999</v>
       </c>
-      <c r="C38" s="27">
+      <c r="C38" s="25">
         <f t="shared" si="0"/>
         <v>3.4890547680944461E-2</v>
       </c>
@@ -10012,13 +10029,13 @@
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A39" s="25">
+      <c r="A39" s="23">
         <v>35124</v>
       </c>
       <c r="B39">
         <v>1.2410999999999901</v>
       </c>
-      <c r="C39" s="27">
+      <c r="C39" s="25">
         <f t="shared" si="0"/>
         <v>5.8351568198395931E-3</v>
       </c>
@@ -10028,13 +10045,13 @@
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A40" s="25">
+      <c r="A40" s="23">
         <v>35153</v>
       </c>
       <c r="B40">
         <v>1.25629999999999</v>
       </c>
-      <c r="C40" s="27">
+      <c r="C40" s="25">
         <f t="shared" si="0"/>
         <v>1.2247200064458896E-2</v>
       </c>
@@ -10044,13 +10061,13 @@
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A41" s="25">
+      <c r="A41" s="23">
         <v>35185</v>
       </c>
       <c r="B41">
         <v>1.2886</v>
       </c>
-      <c r="C41" s="27">
+      <c r="C41" s="25">
         <f t="shared" si="0"/>
         <v>2.5710419485799774E-2</v>
       </c>
@@ -10060,13 +10077,13 @@
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A42" s="25">
+      <c r="A42" s="23">
         <v>35216</v>
       </c>
       <c r="B42">
         <v>1.3099999999999901</v>
       </c>
-      <c r="C42" s="27">
+      <c r="C42" s="25">
         <f t="shared" si="0"/>
         <v>1.6607170572706886E-2</v>
       </c>
@@ -10076,13 +10093,13 @@
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A43" s="25">
+      <c r="A43" s="23">
         <v>35244</v>
       </c>
       <c r="B43">
         <v>1.3230999999999999</v>
       </c>
-      <c r="C43" s="27">
+      <c r="C43" s="25">
         <f t="shared" si="0"/>
         <v>1.0000000000007558E-2</v>
       </c>
@@ -10092,13 +10109,13 @@
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A44" s="25">
+      <c r="A44" s="23">
         <v>35277</v>
       </c>
       <c r="B44">
         <v>1.3263</v>
       </c>
-      <c r="C44" s="27">
+      <c r="C44" s="25">
         <f t="shared" si="0"/>
         <v>2.4185624669337269E-3</v>
       </c>
@@ -10108,13 +10125,13 @@
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A45" s="25">
+      <c r="A45" s="23">
         <v>35307</v>
       </c>
       <c r="B45">
         <v>1.355</v>
       </c>
-      <c r="C45" s="27">
+      <c r="C45" s="25">
         <f t="shared" si="0"/>
         <v>2.1639146497775652E-2</v>
       </c>
@@ -10124,13 +10141,13 @@
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A46" s="25">
+      <c r="A46" s="23">
         <v>35338</v>
       </c>
       <c r="B46">
         <v>1.3852</v>
       </c>
-      <c r="C46" s="27">
+      <c r="C46" s="25">
         <f t="shared" si="0"/>
         <v>2.2287822878228836E-2</v>
       </c>
@@ -10140,13 +10157,13 @@
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A47" s="25">
+      <c r="A47" s="23">
         <v>35369</v>
       </c>
       <c r="B47">
         <v>1.4044999999999901</v>
       </c>
-      <c r="C47" s="27">
+      <c r="C47" s="25">
         <f t="shared" si="0"/>
         <v>1.3933006064099196E-2</v>
       </c>
@@ -10156,13 +10173,13 @@
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A48" s="25">
+      <c r="A48" s="23">
         <v>35398</v>
       </c>
       <c r="B48">
         <v>1.4401999999999999</v>
       </c>
-      <c r="C48" s="27">
+      <c r="C48" s="25">
         <f t="shared" si="0"/>
         <v>2.541829832681386E-2</v>
       </c>
@@ -10172,13 +10189,13 @@
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A49" s="25">
+      <c r="A49" s="23">
         <v>35430</v>
       </c>
       <c r="B49">
         <v>1.4672999999999901</v>
       </c>
-      <c r="C49" s="27">
+      <c r="C49" s="25">
         <f t="shared" si="0"/>
         <v>1.8816830995688205E-2</v>
       </c>
@@ -10188,13 +10205,13 @@
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A50" s="25">
+      <c r="A50" s="23">
         <v>35461</v>
       </c>
       <c r="B50">
         <v>1.5009999999999899</v>
       </c>
-      <c r="C50" s="27">
+      <c r="C50" s="25">
         <f t="shared" si="0"/>
         <v>2.2967355005792944E-2</v>
       </c>
@@ -10204,13 +10221,13 @@
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A51" s="25">
+      <c r="A51" s="23">
         <v>35489</v>
       </c>
       <c r="B51">
         <v>1.5232999999999901</v>
       </c>
-      <c r="C51" s="27">
+      <c r="C51" s="25">
         <f t="shared" si="0"/>
         <v>1.4856762158561132E-2</v>
       </c>
@@ -10220,13 +10237,13 @@
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A52" s="25">
+      <c r="A52" s="23">
         <v>35520</v>
       </c>
       <c r="B52">
         <v>1.52599999999999</v>
       </c>
-      <c r="C52" s="27">
+      <c r="C52" s="25">
         <f t="shared" si="0"/>
         <v>1.7724676688768426E-3</v>
       </c>
@@ -10236,13 +10253,13 @@
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A53" s="25">
+      <c r="A53" s="23">
         <v>35550</v>
       </c>
       <c r="B53">
         <v>1.5310999999999999</v>
       </c>
-      <c r="C53" s="27">
+      <c r="C53" s="25">
         <f t="shared" si="0"/>
         <v>3.3420707732698673E-3</v>
       </c>
@@ -10252,13 +10269,13 @@
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A54" s="25">
+      <c r="A54" s="23">
         <v>35580</v>
       </c>
       <c r="B54">
         <v>1.5756999999999901</v>
       </c>
-      <c r="C54" s="27">
+      <c r="C54" s="25">
         <f t="shared" si="0"/>
         <v>2.9129384102926092E-2</v>
       </c>
@@ -10268,13 +10285,13 @@
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A55" s="25">
+      <c r="A55" s="23">
         <v>35611</v>
       </c>
       <c r="B55">
         <v>1.60249999999999</v>
       </c>
-      <c r="C55" s="27">
+      <c r="C55" s="25">
         <f t="shared" si="0"/>
         <v>1.7008313765310756E-2</v>
       </c>
@@ -10284,13 +10301,13 @@
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A56" s="25">
+      <c r="A56" s="23">
         <v>35642</v>
       </c>
       <c r="B56">
         <v>1.6598999999999999</v>
       </c>
-      <c r="C56" s="27">
+      <c r="C56" s="25">
         <f t="shared" si="0"/>
         <v>3.5819032761316816E-2</v>
       </c>
@@ -10300,13 +10317,13 @@
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A57" s="25">
+      <c r="A57" s="23">
         <v>35671</v>
       </c>
       <c r="B57">
         <v>1.6556</v>
       </c>
-      <c r="C57" s="27">
+      <c r="C57" s="25">
         <f t="shared" si="0"/>
         <v>-2.5905175010542125E-3</v>
       </c>
@@ -10316,13 +10333,13 @@
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A58" s="25">
+      <c r="A58" s="23">
         <v>35703</v>
       </c>
       <c r="B58">
         <v>1.6969999999999901</v>
       </c>
-      <c r="C58" s="27">
+      <c r="C58" s="25">
         <f t="shared" si="0"/>
         <v>2.500604010629992E-2</v>
       </c>
@@ -10332,13 +10349,13 @@
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A59" s="25">
+      <c r="A59" s="23">
         <v>35734</v>
       </c>
       <c r="B59">
         <v>1.7045999999999999</v>
       </c>
-      <c r="C59" s="27">
+      <c r="C59" s="25">
         <f t="shared" si="0"/>
         <v>4.4784914555155986E-3</v>
       </c>
@@ -10348,13 +10365,13 @@
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A60" s="25">
+      <c r="A60" s="23">
         <v>35762</v>
       </c>
       <c r="B60">
         <v>1.7271999999999901</v>
       </c>
-      <c r="C60" s="27">
+      <c r="C60" s="25">
         <f t="shared" si="0"/>
         <v>1.3258242402903964E-2</v>
       </c>
@@ -10364,13 +10381,13 @@
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A61" s="25">
+      <c r="A61" s="23">
         <v>35795</v>
       </c>
       <c r="B61">
         <v>1.7602</v>
       </c>
-      <c r="C61" s="27">
+      <c r="C61" s="25">
         <f t="shared" si="0"/>
         <v>1.9106067623905876E-2</v>
       </c>
@@ -10380,13 +10397,13 @@
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A62" s="25">
+      <c r="A62" s="23">
         <v>35825</v>
       </c>
       <c r="B62">
         <v>1.7907</v>
       </c>
-      <c r="C62" s="27">
+      <c r="C62" s="25">
         <f t="shared" si="0"/>
         <v>1.7327576411771295E-2</v>
       </c>
@@ -10396,13 +10413,13 @@
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A63" s="25">
+      <c r="A63" s="23">
         <v>35853</v>
       </c>
       <c r="B63">
         <v>1.8365</v>
       </c>
-      <c r="C63" s="27">
+      <c r="C63" s="25">
         <f t="shared" si="0"/>
         <v>2.5576590160272472E-2</v>
       </c>
@@ -10412,13 +10429,13 @@
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A64" s="25">
+      <c r="A64" s="23">
         <v>35885</v>
       </c>
       <c r="B64">
         <v>1.8819999999999999</v>
       </c>
-      <c r="C64" s="27">
+      <c r="C64" s="25">
         <f t="shared" si="0"/>
         <v>2.4775387966240014E-2</v>
       </c>
@@ -10428,13 +10445,13 @@
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A65" s="25">
+      <c r="A65" s="23">
         <v>35915</v>
       </c>
       <c r="B65">
         <v>1.8957999999999999</v>
       </c>
-      <c r="C65" s="27">
+      <c r="C65" s="25">
         <f t="shared" si="0"/>
         <v>7.3326248671625738E-3</v>
       </c>
@@ -10444,13 +10461,13 @@
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A66" s="25">
+      <c r="A66" s="23">
         <v>35944</v>
       </c>
       <c r="B66">
         <v>1.8731</v>
       </c>
-      <c r="C66" s="27">
+      <c r="C66" s="25">
         <f t="shared" si="0"/>
         <v>-1.1973836902626878E-2</v>
       </c>
@@ -10460,13 +10477,13 @@
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A67" s="25">
+      <c r="A67" s="23">
         <v>35976</v>
       </c>
       <c r="B67">
         <v>1.8583000000000001</v>
       </c>
-      <c r="C67" s="27">
+      <c r="C67" s="25">
         <f t="shared" si="0"/>
         <v>-7.9013400245582233E-3</v>
       </c>
@@ -10476,13 +10493,13 @@
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A68" s="25">
+      <c r="A68" s="23">
         <v>36007</v>
       </c>
       <c r="B68">
         <v>1.8591</v>
       </c>
-      <c r="C68" s="27">
+      <c r="C68" s="25">
         <f t="shared" si="0"/>
         <v>4.3050099553343379E-4</v>
       </c>
@@ -10492,13 +10509,13 @@
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A69" s="25">
+      <c r="A69" s="23">
         <v>36038</v>
       </c>
       <c r="B69">
         <v>1.6402000000000001</v>
       </c>
-      <c r="C69" s="27">
+      <c r="C69" s="25">
         <f t="shared" si="0"/>
         <v>-0.11774514550051096</v>
       </c>
@@ -10508,13 +10525,13 @@
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A70" s="25">
+      <c r="A70" s="23">
         <v>36068</v>
       </c>
       <c r="B70">
         <v>1.5915999999999999</v>
       </c>
-      <c r="C70" s="27">
+      <c r="C70" s="25">
         <f t="shared" si="0"/>
         <v>-2.9630532861846248E-2</v>
       </c>
@@ -10524,13 +10541,13 @@
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A71" s="25">
+      <c r="A71" s="23">
         <v>36098</v>
       </c>
       <c r="B71">
         <v>1.6021000000000001</v>
       </c>
-      <c r="C71" s="27">
+      <c r="C71" s="25">
         <f t="shared" si="0"/>
         <v>6.5971349585323136E-3</v>
       </c>
@@ -10540,13 +10557,13 @@
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A72" s="25">
+      <c r="A72" s="23">
         <v>36129</v>
       </c>
       <c r="B72">
         <v>1.6463999999999901</v>
       </c>
-      <c r="C72" s="27">
+      <c r="C72" s="25">
         <f t="shared" si="0"/>
         <v>2.7651207789769705E-2</v>
       </c>
@@ -10556,13 +10573,13 @@
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A73" s="25">
+      <c r="A73" s="23">
         <v>36160</v>
       </c>
       <c r="B73">
         <v>1.6744000000000001</v>
       </c>
-      <c r="C73" s="27">
+      <c r="C73" s="25">
         <f t="shared" si="0"/>
         <v>1.700680272109456E-2</v>
       </c>
@@ -10572,13 +10589,13 @@
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A74" s="25">
+      <c r="A74" s="23">
         <v>36189</v>
       </c>
       <c r="B74">
         <v>1.7058</v>
       </c>
-      <c r="C74" s="27">
+      <c r="C74" s="25">
         <f t="shared" si="0"/>
         <v>1.8752986144290329E-2</v>
       </c>
@@ -10588,13 +10605,13 @@
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A75" s="25">
+      <c r="A75" s="23">
         <v>36217</v>
       </c>
       <c r="B75">
         <v>1.7050000000000001</v>
       </c>
-      <c r="C75" s="27">
+      <c r="C75" s="25">
         <f t="shared" si="0"/>
         <v>-4.6898815804896632E-4</v>
       </c>
@@ -10604,13 +10621,13 @@
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A76" s="25">
+      <c r="A76" s="23">
         <v>36250</v>
       </c>
       <c r="B76">
         <v>1.7458</v>
       </c>
-      <c r="C76" s="27">
+      <c r="C76" s="25">
         <f t="shared" si="0"/>
         <v>2.3929618768328442E-2</v>
       </c>
@@ -10620,13 +10637,13 @@
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A77" s="25">
+      <c r="A77" s="23">
         <v>36280</v>
       </c>
       <c r="B77">
         <v>1.7993999999999899</v>
       </c>
-      <c r="C77" s="27">
+      <c r="C77" s="25">
         <f t="shared" si="0"/>
         <v>3.0702256844993725E-2</v>
       </c>
@@ -10636,13 +10653,13 @@
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A78" s="25">
+      <c r="A78" s="23">
         <v>36311</v>
       </c>
       <c r="B78">
         <v>1.83849999999999</v>
       </c>
-      <c r="C78" s="27">
+      <c r="C78" s="25">
         <f t="shared" si="0"/>
         <v>2.1729465377348101E-2</v>
       </c>
@@ -10652,13 +10669,13 @@
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A79" s="25">
+      <c r="A79" s="23">
         <v>36341</v>
       </c>
       <c r="B79">
         <v>1.8922999999999901</v>
       </c>
-      <c r="C79" s="27">
+      <c r="C79" s="25">
         <f t="shared" ref="C79:C142" si="3">B79/B78-1</f>
         <v>2.9262986129997559E-2</v>
       </c>
@@ -10668,13 +10685,13 @@
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A80" s="25">
+      <c r="A80" s="23">
         <v>36371</v>
       </c>
       <c r="B80">
         <v>1.91719999999999</v>
       </c>
-      <c r="C80" s="27">
+      <c r="C80" s="25">
         <f t="shared" si="3"/>
         <v>1.3158590075569521E-2</v>
       </c>
@@ -10684,13 +10701,13 @@
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A81" s="25">
+      <c r="A81" s="23">
         <v>36403</v>
       </c>
       <c r="B81">
         <v>1.91929999999999</v>
       </c>
-      <c r="C81" s="27">
+      <c r="C81" s="25">
         <f t="shared" si="3"/>
         <v>1.0953473815982218E-3</v>
       </c>
@@ -10700,13 +10717,13 @@
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A82" s="25">
+      <c r="A82" s="23">
         <v>36433</v>
       </c>
       <c r="B82">
         <v>1.93919999999999</v>
       </c>
-      <c r="C82" s="27">
+      <c r="C82" s="25">
         <f t="shared" si="3"/>
         <v>1.0368363465846908E-2</v>
       </c>
@@ -10716,13 +10733,13 @@
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A83" s="25">
+      <c r="A83" s="23">
         <v>36462</v>
       </c>
       <c r="B83">
         <v>1.946</v>
       </c>
-      <c r="C83" s="27">
+      <c r="C83" s="25">
         <f t="shared" si="3"/>
         <v>3.5066006600710242E-3</v>
       </c>
@@ -10732,13 +10749,13 @@
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A84" s="25">
+      <c r="A84" s="23">
         <v>36494</v>
       </c>
       <c r="B84">
         <v>1.9857</v>
       </c>
-      <c r="C84" s="27">
+      <c r="C84" s="25">
         <f t="shared" si="3"/>
         <v>2.0400822199383439E-2</v>
       </c>
@@ -10748,13 +10765,13 @@
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A85" s="25">
+      <c r="A85" s="23">
         <v>36525</v>
       </c>
       <c r="B85">
         <v>2.0470999999999999</v>
       </c>
-      <c r="C85" s="27">
+      <c r="C85" s="25">
         <f t="shared" si="3"/>
         <v>3.0921085763206957E-2</v>
       </c>
@@ -10764,13 +10781,13 @@
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A86" s="25">
+      <c r="A86" s="23">
         <v>36556</v>
       </c>
       <c r="B86">
         <v>2.0575999999999999</v>
       </c>
-      <c r="C86" s="27">
+      <c r="C86" s="25">
         <f t="shared" si="3"/>
         <v>5.1292071711201981E-3</v>
       </c>
@@ -10780,13 +10797,13 @@
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A87" s="25">
+      <c r="A87" s="23">
         <v>36585</v>
       </c>
       <c r="B87">
         <v>2.105</v>
       </c>
-      <c r="C87" s="27">
+      <c r="C87" s="25">
         <f t="shared" si="3"/>
         <v>2.3036547433903598E-2</v>
       </c>
@@ -10796,13 +10813,13 @@
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A88" s="25">
+      <c r="A88" s="23">
         <v>36616</v>
       </c>
       <c r="B88">
         <v>2.1177000000000001</v>
       </c>
-      <c r="C88" s="27">
+      <c r="C88" s="25">
         <f t="shared" si="3"/>
         <v>6.0332541567695852E-3</v>
       </c>
@@ -10812,13 +10829,13 @@
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A89" s="25">
+      <c r="A89" s="23">
         <v>36644</v>
       </c>
       <c r="B89">
         <v>2.1021999999999998</v>
       </c>
-      <c r="C89" s="27">
+      <c r="C89" s="25">
         <f t="shared" si="3"/>
         <v>-7.3192614629079555E-3</v>
       </c>
@@ -10828,13 +10845,13 @@
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A90" s="25">
+      <c r="A90" s="23">
         <v>36677</v>
       </c>
       <c r="B90">
         <v>2.1027</v>
       </c>
-      <c r="C90" s="27">
+      <c r="C90" s="25">
         <f t="shared" si="3"/>
         <v>2.3784606602617053E-4</v>
       </c>
@@ -10844,13 +10861,13 @@
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A91" s="25">
+      <c r="A91" s="23">
         <v>36707</v>
       </c>
       <c r="B91">
         <v>2.14339999999999</v>
       </c>
-      <c r="C91" s="27">
+      <c r="C91" s="25">
         <f t="shared" si="3"/>
         <v>1.9356066010362882E-2</v>
       </c>
@@ -10860,13 +10877,13 @@
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A92" s="25">
+      <c r="A92" s="23">
         <v>36738</v>
       </c>
       <c r="B92">
         <v>2.1540999999999899</v>
       </c>
-      <c r="C92" s="27">
+      <c r="C92" s="25">
         <f t="shared" si="3"/>
         <v>4.9920686759354904E-3</v>
       </c>
@@ -10876,13 +10893,13 @@
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A93" s="25">
+      <c r="A93" s="23">
         <v>36769</v>
       </c>
       <c r="B93">
         <v>2.1909999999999901</v>
       </c>
-      <c r="C93" s="27">
+      <c r="C93" s="25">
         <f t="shared" si="3"/>
         <v>1.71301239496775E-2</v>
       </c>
@@ -10892,13 +10909,13 @@
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A94" s="25">
+      <c r="A94" s="23">
         <v>36798</v>
       </c>
       <c r="B94">
         <v>2.2043999999999899</v>
       </c>
-      <c r="C94" s="27">
+      <c r="C94" s="25">
         <f t="shared" si="3"/>
         <v>6.115928799634851E-3</v>
       </c>
@@ -10908,13 +10925,13 @@
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A95" s="25">
+      <c r="A95" s="23">
         <v>36830</v>
       </c>
       <c r="B95">
         <v>2.20339999999999</v>
       </c>
-      <c r="C95" s="27">
+      <c r="C95" s="25">
         <f t="shared" si="3"/>
         <v>-4.5363817818899754E-4</v>
       </c>
@@ -10924,13 +10941,13 @@
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A96" s="25">
+      <c r="A96" s="23">
         <v>36860</v>
       </c>
       <c r="B96">
         <v>2.1864999999999899</v>
       </c>
-      <c r="C96" s="27">
+      <c r="C96" s="25">
         <f t="shared" si="3"/>
         <v>-7.6699646001634481E-3</v>
       </c>
@@ -10940,13 +10957,13 @@
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A97" s="25">
+      <c r="A97" s="23">
         <v>36889</v>
       </c>
       <c r="B97">
         <v>2.1956999999999902</v>
       </c>
-      <c r="C97" s="27">
+      <c r="C97" s="25">
         <f t="shared" si="3"/>
         <v>4.2076377772697349E-3</v>
       </c>
@@ -10956,13 +10973,13 @@
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A98" s="25">
+      <c r="A98" s="23">
         <v>36922</v>
       </c>
       <c r="B98">
         <v>2.2497999999999898</v>
       </c>
-      <c r="C98" s="27">
+      <c r="C98" s="25">
         <f t="shared" si="3"/>
         <v>2.4639067267841597E-2</v>
       </c>
@@ -10972,13 +10989,13 @@
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A99" s="25">
+      <c r="A99" s="23">
         <v>36950</v>
       </c>
       <c r="B99">
         <v>2.2854999999999901</v>
       </c>
-      <c r="C99" s="27">
+      <c r="C99" s="25">
         <f t="shared" si="3"/>
         <v>1.5868077162414673E-2</v>
       </c>
@@ -10988,13 +11005,13 @@
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A100" s="25">
+      <c r="A100" s="23">
         <v>36980</v>
       </c>
       <c r="B100">
         <v>2.28819999999999</v>
       </c>
-      <c r="C100" s="27">
+      <c r="C100" s="25">
         <f t="shared" si="3"/>
         <v>1.1813607525705816E-3</v>
       </c>
@@ -11004,13 +11021,13 @@
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A101" s="25">
+      <c r="A101" s="23">
         <v>37011</v>
       </c>
       <c r="B101">
         <v>2.3093999999999899</v>
       </c>
-      <c r="C101" s="27">
+      <c r="C101" s="25">
         <f t="shared" si="3"/>
         <v>9.2649243947207083E-3</v>
       </c>
@@ -11020,13 +11037,13 @@
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A102" s="25">
+      <c r="A102" s="23">
         <v>37042</v>
       </c>
       <c r="B102">
         <v>2.33489999999999</v>
       </c>
-      <c r="C102" s="27">
+      <c r="C102" s="25">
         <f t="shared" si="3"/>
         <v>1.1041829046505747E-2</v>
       </c>
@@ -11036,13 +11053,13 @@
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A103" s="25">
+      <c r="A103" s="23">
         <v>37071</v>
       </c>
       <c r="B103">
         <v>2.35889999999999</v>
       </c>
-      <c r="C103" s="27">
+      <c r="C103" s="25">
         <f t="shared" si="3"/>
         <v>1.0278812797122061E-2</v>
       </c>
@@ -11052,13 +11069,13 @@
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A104" s="25">
+      <c r="A104" s="23">
         <v>37103</v>
       </c>
       <c r="B104">
         <v>2.3700999999999901</v>
       </c>
-      <c r="C104" s="27">
+      <c r="C104" s="25">
         <f t="shared" si="3"/>
         <v>4.7479757514097276E-3</v>
       </c>
@@ -11068,13 +11085,13 @@
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A105" s="25">
+      <c r="A105" s="23">
         <v>37134</v>
       </c>
       <c r="B105">
         <v>2.40689999999999</v>
       </c>
-      <c r="C105" s="27">
+      <c r="C105" s="25">
         <f t="shared" si="3"/>
         <v>1.5526771022319696E-2</v>
       </c>
@@ -11084,13 +11101,13 @@
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A106" s="25">
+      <c r="A106" s="23">
         <v>37162</v>
       </c>
       <c r="B106">
         <v>2.3697999999999899</v>
       </c>
-      <c r="C106" s="27">
+      <c r="C106" s="25">
         <f t="shared" si="3"/>
         <v>-1.5414018031492893E-2</v>
       </c>
@@ -11100,13 +11117,13 @@
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A107" s="25">
+      <c r="A107" s="23">
         <v>37195</v>
       </c>
       <c r="B107">
         <v>2.4018999999999902</v>
       </c>
-      <c r="C107" s="27">
+      <c r="C107" s="25">
         <f t="shared" si="3"/>
         <v>1.3545446873153955E-2</v>
       </c>
@@ -11116,13 +11133,13 @@
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A108" s="25">
+      <c r="A108" s="23">
         <v>37225</v>
       </c>
       <c r="B108">
         <v>2.4221999999999899</v>
       </c>
-      <c r="C108" s="27">
+      <c r="C108" s="25">
         <f t="shared" si="3"/>
         <v>8.4516424497271814E-3</v>
       </c>
@@ -11132,13 +11149,13 @@
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A109" s="25">
+      <c r="A109" s="23">
         <v>37256</v>
       </c>
       <c r="B109">
         <v>2.44809999999999</v>
       </c>
-      <c r="C109" s="27">
+      <c r="C109" s="25">
         <f t="shared" si="3"/>
         <v>1.0692758649162082E-2</v>
       </c>
@@ -11148,13 +11165,13 @@
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A110" s="25">
+      <c r="A110" s="23">
         <v>37287</v>
       </c>
       <c r="B110">
         <v>2.4770999999999899</v>
       </c>
-      <c r="C110" s="27">
+      <c r="C110" s="25">
         <f t="shared" si="3"/>
         <v>1.1845921326743225E-2</v>
       </c>
@@ -11164,13 +11181,13 @@
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A111" s="25">
+      <c r="A111" s="23">
         <v>37315</v>
       </c>
       <c r="B111">
         <v>2.4686999999999899</v>
       </c>
-      <c r="C111" s="27">
+      <c r="C111" s="25">
         <f t="shared" si="3"/>
         <v>-3.3910621291025622E-3</v>
       </c>
@@ -11180,13 +11197,13 @@
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A112" s="25">
+      <c r="A112" s="23">
         <v>37344</v>
       </c>
       <c r="B112">
         <v>2.49799999999999</v>
       </c>
-      <c r="C112" s="27">
+      <c r="C112" s="25">
         <f t="shared" si="3"/>
         <v>1.1868594806983435E-2</v>
       </c>
@@ -11196,13 +11213,13 @@
       </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A113" s="25">
+      <c r="A113" s="23">
         <v>37376</v>
       </c>
       <c r="B113">
         <v>2.5163999999999902</v>
       </c>
-      <c r="C113" s="27">
+      <c r="C113" s="25">
         <f t="shared" si="3"/>
         <v>7.3658927141715402E-3</v>
       </c>
@@ -11212,13 +11229,13 @@
       </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A114" s="25">
+      <c r="A114" s="23">
         <v>37407</v>
       </c>
       <c r="B114">
         <v>2.5192999999999901</v>
       </c>
-      <c r="C114" s="27">
+      <c r="C114" s="25">
         <f t="shared" si="3"/>
         <v>1.1524399936417851E-3</v>
       </c>
@@ -11228,13 +11245,13 @@
       </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A115" s="25">
+      <c r="A115" s="23">
         <v>37435</v>
       </c>
       <c r="B115">
         <v>2.44559999999999</v>
       </c>
-      <c r="C115" s="27">
+      <c r="C115" s="25">
         <f t="shared" si="3"/>
         <v>-2.9254157901004385E-2</v>
       </c>
@@ -11244,13 +11261,13 @@
       </c>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A116" s="25">
+      <c r="A116" s="23">
         <v>37468</v>
       </c>
       <c r="B116">
         <v>2.3696999999999901</v>
       </c>
-      <c r="C116" s="27">
+      <c r="C116" s="25">
         <f t="shared" si="3"/>
         <v>-3.1035328753680091E-2</v>
       </c>
@@ -11260,13 +11277,13 @@
       </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A117" s="25">
+      <c r="A117" s="23">
         <v>37498</v>
       </c>
       <c r="B117">
         <v>2.3760999999999899</v>
       </c>
-      <c r="C117" s="27">
+      <c r="C117" s="25">
         <f t="shared" si="3"/>
         <v>2.7007638097649167E-3</v>
       </c>
@@ -11276,13 +11293,13 @@
       </c>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A118" s="25">
+      <c r="A118" s="23">
         <v>37529</v>
       </c>
       <c r="B118">
         <v>2.3713999999999902</v>
       </c>
-      <c r="C118" s="27">
+      <c r="C118" s="25">
         <f t="shared" si="3"/>
         <v>-1.978031227641841E-3</v>
       </c>
@@ -11292,13 +11309,13 @@
       </c>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A119" s="25">
+      <c r="A119" s="23">
         <v>37560</v>
       </c>
       <c r="B119">
         <v>2.3671999999999902</v>
       </c>
-      <c r="C119" s="27">
+      <c r="C119" s="25">
         <f t="shared" si="3"/>
         <v>-1.7711056759720512E-3</v>
       </c>
@@ -11308,13 +11325,13 @@
       </c>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A120" s="25">
+      <c r="A120" s="23">
         <v>37589</v>
       </c>
       <c r="B120">
         <v>2.4279999999999902</v>
       </c>
-      <c r="C120" s="27">
+      <c r="C120" s="25">
         <f t="shared" si="3"/>
         <v>2.5684352821899292E-2</v>
       </c>
@@ -11324,13 +11341,13 @@
       </c>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A121" s="25">
+      <c r="A121" s="23">
         <v>37621</v>
       </c>
       <c r="B121">
         <v>2.4519999999999902</v>
       </c>
-      <c r="C121" s="27">
+      <c r="C121" s="25">
         <f t="shared" si="3"/>
         <v>9.884678747940745E-3</v>
       </c>
@@ -11340,13 +11357,13 @@
       </c>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A122" s="25">
+      <c r="A122" s="23">
         <v>37652</v>
       </c>
       <c r="B122">
         <v>2.5075999999999898</v>
       </c>
-      <c r="C122" s="27">
+      <c r="C122" s="25">
         <f t="shared" si="3"/>
         <v>2.2675367047308326E-2</v>
       </c>
@@ -11356,13 +11373,13 @@
       </c>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A123" s="25">
+      <c r="A123" s="23">
         <v>37680</v>
       </c>
       <c r="B123">
         <v>2.5233999999999899</v>
       </c>
-      <c r="C123" s="27">
+      <c r="C123" s="25">
         <f t="shared" si="3"/>
         <v>6.300845429893176E-3</v>
       </c>
@@ -11372,13 +11389,13 @@
       </c>
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A124" s="25">
+      <c r="A124" s="23">
         <v>37711</v>
       </c>
       <c r="B124">
         <v>2.5487999999999902</v>
       </c>
-      <c r="C124" s="27">
+      <c r="C124" s="25">
         <f t="shared" si="3"/>
         <v>1.00657842593328E-2</v>
       </c>
@@ -11388,13 +11405,13 @@
       </c>
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A125" s="25">
+      <c r="A125" s="23">
         <v>37741</v>
       </c>
       <c r="B125">
         <v>2.61289999999999</v>
       </c>
-      <c r="C125" s="27">
+      <c r="C125" s="25">
         <f t="shared" si="3"/>
         <v>2.5149089767733779E-2</v>
       </c>
@@ -11404,13 +11421,13 @@
       </c>
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A126" s="25">
+      <c r="A126" s="23">
         <v>37771</v>
       </c>
       <c r="B126">
         <v>2.6742999999999899</v>
       </c>
-      <c r="C126" s="27">
+      <c r="C126" s="25">
         <f t="shared" si="3"/>
         <v>2.3498794442956106E-2</v>
       </c>
@@ -11420,13 +11437,13 @@
       </c>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A127" s="25">
+      <c r="A127" s="23">
         <v>37802</v>
       </c>
       <c r="B127">
         <v>2.7224999999999899</v>
       </c>
-      <c r="C127" s="27">
+      <c r="C127" s="25">
         <f t="shared" si="3"/>
         <v>1.8023407994615548E-2</v>
       </c>
@@ -11436,13 +11453,13 @@
       </c>
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A128" s="25">
+      <c r="A128" s="23">
         <v>37833</v>
       </c>
       <c r="B128">
         <v>2.7482999999999902</v>
       </c>
-      <c r="C128" s="27">
+      <c r="C128" s="25">
         <f t="shared" si="3"/>
         <v>9.4765840220387698E-3</v>
       </c>
@@ -11452,13 +11469,13 @@
       </c>
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A129" s="25">
+      <c r="A129" s="23">
         <v>37862</v>
       </c>
       <c r="B129">
         <v>2.7718999999999898</v>
       </c>
-      <c r="C129" s="27">
+      <c r="C129" s="25">
         <f t="shared" si="3"/>
         <v>8.5871265873447289E-3</v>
       </c>
@@ -11468,13 +11485,13 @@
       </c>
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A130" s="25">
+      <c r="A130" s="23">
         <v>37894</v>
       </c>
       <c r="B130">
         <v>2.8217999999999899</v>
       </c>
-      <c r="C130" s="27">
+      <c r="C130" s="25">
         <f t="shared" si="3"/>
         <v>1.8002092427576777E-2</v>
       </c>
@@ -11484,13 +11501,13 @@
       </c>
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A131" s="25">
+      <c r="A131" s="23">
         <v>37925</v>
       </c>
       <c r="B131">
         <v>2.8650999999999902</v>
       </c>
-      <c r="C131" s="27">
+      <c r="C131" s="25">
         <f t="shared" si="3"/>
         <v>1.5344815366078457E-2</v>
       </c>
@@ -11500,13 +11517,13 @@
       </c>
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A132" s="25">
+      <c r="A132" s="23">
         <v>37953</v>
       </c>
       <c r="B132">
         <v>2.8997999999999902</v>
       </c>
-      <c r="C132" s="27">
+      <c r="C132" s="25">
         <f t="shared" si="3"/>
         <v>1.2111270112736161E-2</v>
       </c>
@@ -11516,13 +11533,13 @@
       </c>
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A133" s="25">
+      <c r="A133" s="23">
         <v>37986</v>
       </c>
       <c r="B133">
         <v>2.9428999999999901</v>
       </c>
-      <c r="C133" s="27">
+      <c r="C133" s="25">
         <f t="shared" si="3"/>
         <v>1.4863094006483335E-2</v>
       </c>
@@ -11532,13 +11549,13 @@
       </c>
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A134" s="25">
+      <c r="A134" s="23">
         <v>38016</v>
       </c>
       <c r="B134">
         <v>3.00639999999999</v>
       </c>
-      <c r="C134" s="27">
+      <c r="C134" s="25">
         <f t="shared" si="3"/>
         <v>2.1577355669577747E-2</v>
       </c>
@@ -11548,13 +11565,13 @@
       </c>
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A135" s="25">
+      <c r="A135" s="23">
         <v>38044</v>
       </c>
       <c r="B135">
         <v>3.0348999999999902</v>
       </c>
-      <c r="C135" s="27">
+      <c r="C135" s="25">
         <f t="shared" si="3"/>
         <v>9.4797764768494996E-3</v>
       </c>
@@ -11564,13 +11581,13 @@
       </c>
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A136" s="25">
+      <c r="A136" s="23">
         <v>38077</v>
       </c>
       <c r="B136">
         <v>3.0485999999999902</v>
       </c>
-      <c r="C136" s="27">
+      <c r="C136" s="25">
         <f t="shared" si="3"/>
         <v>4.5141520313685124E-3</v>
       </c>
@@ -11580,13 +11597,13 @@
       </c>
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A137" s="25">
+      <c r="A137" s="23">
         <v>38107</v>
       </c>
       <c r="B137">
         <v>3.06429999999999</v>
       </c>
-      <c r="C137" s="27">
+      <c r="C137" s="25">
         <f t="shared" si="3"/>
         <v>5.149904874368616E-3</v>
       </c>
@@ -11596,13 +11613,13 @@
       </c>
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A138" s="25">
+      <c r="A138" s="23">
         <v>38138</v>
       </c>
       <c r="B138">
         <v>3.0671999999999899</v>
       </c>
-      <c r="C138" s="27">
+      <c r="C138" s="25">
         <f t="shared" si="3"/>
         <v>9.4638253434720099E-4</v>
       </c>
@@ -11612,13 +11629,13 @@
       </c>
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A139" s="25">
+      <c r="A139" s="23">
         <v>38168</v>
       </c>
       <c r="B139">
         <v>3.09669999999999</v>
       </c>
-      <c r="C139" s="27">
+      <c r="C139" s="25">
         <f t="shared" si="3"/>
         <v>9.6178925404277749E-3</v>
       </c>
@@ -11628,13 +11645,13 @@
       </c>
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A140" s="25">
+      <c r="A140" s="23">
         <v>38198</v>
       </c>
       <c r="B140">
         <v>3.0967999999999898</v>
       </c>
-      <c r="C140" s="27">
+      <c r="C140" s="25">
         <f t="shared" si="3"/>
         <v>3.2292440339531936E-5</v>
       </c>
@@ -11644,13 +11661,13 @@
       </c>
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A141" s="25">
+      <c r="A141" s="23">
         <v>38230</v>
       </c>
       <c r="B141">
         <v>3.11079999999999</v>
       </c>
-      <c r="C141" s="27">
+      <c r="C141" s="25">
         <f t="shared" si="3"/>
         <v>4.5207956600361587E-3</v>
       </c>
@@ -11660,13 +11677,13 @@
       </c>
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A142" s="25">
+      <c r="A142" s="23">
         <v>38260</v>
       </c>
       <c r="B142">
         <v>3.1501999999999901</v>
       </c>
-      <c r="C142" s="27">
+      <c r="C142" s="25">
         <f t="shared" si="3"/>
         <v>1.2665552269512714E-2</v>
       </c>
@@ -11676,13 +11693,13 @@
       </c>
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A143" s="25">
+      <c r="A143" s="23">
         <v>38289</v>
       </c>
       <c r="B143">
         <v>3.1891999999999898</v>
       </c>
-      <c r="C143" s="27">
+      <c r="C143" s="25">
         <f t="shared" ref="C143:C206" si="5">B143/B142-1</f>
         <v>1.2380166338645138E-2</v>
       </c>
@@ -11692,13 +11709,13 @@
       </c>
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A144" s="25">
+      <c r="A144" s="23">
         <v>38321</v>
       </c>
       <c r="B144">
         <v>3.2935999999999899</v>
       </c>
-      <c r="C144" s="27">
+      <c r="C144" s="25">
         <f t="shared" si="5"/>
         <v>3.2735482252602699E-2</v>
       </c>
@@ -11708,13 +11725,13 @@
       </c>
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A145" s="25">
+      <c r="A145" s="23">
         <v>38352</v>
       </c>
       <c r="B145">
         <v>3.36859999999999</v>
       </c>
-      <c r="C145" s="27">
+      <c r="C145" s="25">
         <f t="shared" si="5"/>
         <v>2.277143551129468E-2</v>
       </c>
@@ -11724,13 +11741,13 @@
       </c>
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A146" s="25">
+      <c r="A146" s="23">
         <v>38383</v>
       </c>
       <c r="B146">
         <v>3.3753999999999902</v>
       </c>
-      <c r="C146" s="27">
+      <c r="C146" s="25">
         <f t="shared" si="5"/>
         <v>2.0186427596033951E-3</v>
       </c>
@@ -11740,13 +11757,13 @@
       </c>
     </row>
     <row r="147" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A147" s="25">
+      <c r="A147" s="23">
         <v>38411</v>
       </c>
       <c r="B147">
         <v>3.4289999999999901</v>
       </c>
-      <c r="C147" s="27">
+      <c r="C147" s="25">
         <f t="shared" si="5"/>
         <v>1.5879599454879489E-2</v>
       </c>
@@ -11756,13 +11773,13 @@
       </c>
     </row>
     <row r="148" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A148" s="25">
+      <c r="A148" s="23">
         <v>38442</v>
       </c>
       <c r="B148">
         <v>3.4486999999999899</v>
       </c>
-      <c r="C148" s="27">
+      <c r="C148" s="25">
         <f t="shared" si="5"/>
         <v>5.7451151939340583E-3</v>
       </c>
@@ -11772,13 +11789,13 @@
       </c>
     </row>
     <row r="149" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A149" s="25">
+      <c r="A149" s="23">
         <v>38471</v>
       </c>
       <c r="B149">
         <v>3.4265999999999899</v>
       </c>
-      <c r="C149" s="27">
+      <c r="C149" s="25">
         <f t="shared" si="5"/>
         <v>-6.4082117899498803E-3</v>
       </c>
@@ -11788,13 +11805,13 @@
       </c>
     </row>
     <row r="150" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A150" s="25">
+      <c r="A150" s="23">
         <v>38503</v>
       </c>
       <c r="B150">
         <v>3.44559999999999</v>
       </c>
-      <c r="C150" s="27">
+      <c r="C150" s="25">
         <f t="shared" si="5"/>
         <v>5.5448549582677309E-3</v>
       </c>
@@ -11804,13 +11821,13 @@
       </c>
     </row>
     <row r="151" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A151" s="25">
+      <c r="A151" s="23">
         <v>38533</v>
       </c>
       <c r="B151">
         <v>3.48999999999999</v>
       </c>
-      <c r="C151" s="27">
+      <c r="C151" s="25">
         <f t="shared" si="5"/>
         <v>1.2885999535639625E-2</v>
       </c>
@@ -11820,13 +11837,13 @@
       </c>
     </row>
     <row r="152" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A152" s="25">
+      <c r="A152" s="23">
         <v>38562</v>
       </c>
       <c r="B152">
         <v>3.5690999999999899</v>
       </c>
-      <c r="C152" s="27">
+      <c r="C152" s="25">
         <f t="shared" si="5"/>
         <v>2.2664756446991507E-2</v>
       </c>
@@ -11836,13 +11853,13 @@
       </c>
     </row>
     <row r="153" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A153" s="25">
+      <c r="A153" s="23">
         <v>38595</v>
       </c>
       <c r="B153">
         <v>3.5994999999999902</v>
       </c>
-      <c r="C153" s="27">
+      <c r="C153" s="25">
         <f t="shared" si="5"/>
         <v>8.5175534448460599E-3</v>
       </c>
@@ -11852,13 +11869,13 @@
       </c>
     </row>
     <row r="154" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A154" s="25">
+      <c r="A154" s="23">
         <v>38625</v>
       </c>
       <c r="B154">
         <v>3.6380999999999899</v>
       </c>
-      <c r="C154" s="27">
+      <c r="C154" s="25">
         <f t="shared" si="5"/>
         <v>1.0723711626614785E-2</v>
       </c>
@@ -11868,13 +11885,13 @@
       </c>
     </row>
     <row r="155" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A155" s="25">
+      <c r="A155" s="23">
         <v>38656</v>
       </c>
       <c r="B155">
         <v>3.5719999999999898</v>
       </c>
-      <c r="C155" s="27">
+      <c r="C155" s="25">
         <f t="shared" si="5"/>
         <v>-1.8168824386355586E-2</v>
       </c>
@@ -11884,13 +11901,13 @@
       </c>
     </row>
     <row r="156" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A156" s="25">
+      <c r="A156" s="23">
         <v>38686</v>
       </c>
       <c r="B156">
         <v>3.6175999999999902</v>
       </c>
-      <c r="C156" s="27">
+      <c r="C156" s="25">
         <f t="shared" si="5"/>
         <v>1.276595744680864E-2</v>
       </c>
@@ -11900,13 +11917,13 @@
       </c>
     </row>
     <row r="157" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A157" s="25">
+      <c r="A157" s="23">
         <v>38716</v>
       </c>
       <c r="B157">
         <v>3.6701999999999901</v>
       </c>
-      <c r="C157" s="27">
+      <c r="C157" s="25">
         <f t="shared" si="5"/>
         <v>1.454002653693065E-2</v>
       </c>
@@ -11916,13 +11933,13 @@
       </c>
     </row>
     <row r="158" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A158" s="25">
+      <c r="A158" s="23">
         <v>38748</v>
       </c>
       <c r="B158">
         <v>3.7772999999999901</v>
       </c>
-      <c r="C158" s="27">
+      <c r="C158" s="25">
         <f t="shared" si="5"/>
         <v>2.9180971064247219E-2</v>
       </c>
@@ -11932,13 +11949,13 @@
       </c>
     </row>
     <row r="159" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A159" s="25">
+      <c r="A159" s="23">
         <v>38776</v>
       </c>
       <c r="B159">
         <v>3.7901999999999898</v>
       </c>
-      <c r="C159" s="27">
+      <c r="C159" s="25">
         <f t="shared" si="5"/>
         <v>3.4151377968389962E-3</v>
       </c>
@@ -11948,13 +11965,13 @@
       </c>
     </row>
     <row r="160" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A160" s="25">
+      <c r="A160" s="23">
         <v>38807</v>
       </c>
       <c r="B160">
         <v>3.84689999999999</v>
       </c>
-      <c r="C160" s="27">
+      <c r="C160" s="25">
         <f t="shared" si="5"/>
         <v>1.4959632737058914E-2</v>
       </c>
@@ -11964,13 +11981,13 @@
       </c>
     </row>
     <row r="161" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A161" s="25">
+      <c r="A161" s="23">
         <v>38835</v>
       </c>
       <c r="B161">
         <v>3.9140999999999901</v>
       </c>
-      <c r="C161" s="27">
+      <c r="C161" s="25">
         <f t="shared" si="5"/>
         <v>1.7468611089448638E-2</v>
       </c>
@@ -11980,13 +11997,13 @@
       </c>
     </row>
     <row r="162" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A162" s="25">
+      <c r="A162" s="23">
         <v>38868</v>
       </c>
       <c r="B162">
         <v>3.9106999999999901</v>
       </c>
-      <c r="C162" s="27">
+      <c r="C162" s="25">
         <f t="shared" si="5"/>
         <v>-8.6865435221383791E-4</v>
       </c>
@@ -11996,13 +12013,13 @@
       </c>
     </row>
     <row r="163" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A163" s="25">
+      <c r="A163" s="23">
         <v>38898</v>
       </c>
       <c r="B163">
         <v>3.93989999999999</v>
       </c>
-      <c r="C163" s="27">
+      <c r="C163" s="25">
         <f t="shared" si="5"/>
         <v>7.4666939422609602E-3</v>
       </c>
@@ -12012,13 +12029,13 @@
       </c>
     </row>
     <row r="164" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A164" s="25">
+      <c r="A164" s="23">
         <v>38929</v>
       </c>
       <c r="B164">
         <v>3.94139999999999</v>
       </c>
-      <c r="C164" s="27">
+      <c r="C164" s="25">
         <f t="shared" si="5"/>
         <v>3.8072032285074719E-4</v>
       </c>
@@ -12028,13 +12045,13 @@
       </c>
     </row>
     <row r="165" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A165" s="25">
+      <c r="A165" s="23">
         <v>38960</v>
       </c>
       <c r="B165">
         <v>3.9827999999999899</v>
       </c>
-      <c r="C165" s="27">
+      <c r="C165" s="25">
         <f t="shared" si="5"/>
         <v>1.0503881869386555E-2</v>
       </c>
@@ -12044,13 +12061,13 @@
       </c>
     </row>
     <row r="166" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A166" s="25">
+      <c r="A166" s="23">
         <v>38989</v>
       </c>
       <c r="B166">
         <v>4.0064999999999902</v>
       </c>
-      <c r="C166" s="27">
+      <c r="C166" s="25">
         <f t="shared" si="5"/>
         <v>5.95058752636346E-3</v>
       </c>
@@ -12060,13 +12077,13 @@
       </c>
     </row>
     <row r="167" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A167" s="25">
+      <c r="A167" s="23">
         <v>39021</v>
       </c>
       <c r="B167">
         <v>4.0956999999999901</v>
       </c>
-      <c r="C167" s="27">
+      <c r="C167" s="25">
         <f t="shared" si="5"/>
         <v>2.2263821290403163E-2</v>
       </c>
@@ -12076,13 +12093,13 @@
       </c>
     </row>
     <row r="168" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A168" s="25">
+      <c r="A168" s="23">
         <v>39051</v>
       </c>
       <c r="B168">
         <v>4.1811999999999898</v>
       </c>
-      <c r="C168" s="27">
+      <c r="C168" s="25">
         <f t="shared" si="5"/>
         <v>2.087555240862371E-2</v>
       </c>
@@ -12092,13 +12109,13 @@
       </c>
     </row>
     <row r="169" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A169" s="25">
+      <c r="A169" s="23">
         <v>39080</v>
       </c>
       <c r="B169">
         <v>4.2473999999999901</v>
       </c>
-      <c r="C169" s="27">
+      <c r="C169" s="25">
         <f t="shared" si="5"/>
         <v>1.5832775279824185E-2</v>
       </c>
@@ -12108,13 +12125,13 @@
       </c>
     </row>
     <row r="170" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A170" s="25">
+      <c r="A170" s="23">
         <v>39113</v>
       </c>
       <c r="B170">
         <v>4.3349999999999902</v>
       </c>
-      <c r="C170" s="27">
+      <c r="C170" s="25">
         <f t="shared" si="5"/>
         <v>2.0624381974855277E-2</v>
       </c>
@@ -12124,13 +12141,13 @@
       </c>
     </row>
     <row r="171" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A171" s="25">
+      <c r="A171" s="23">
         <v>39141</v>
       </c>
       <c r="B171">
         <v>4.4021999999999899</v>
       </c>
-      <c r="C171" s="27">
+      <c r="C171" s="25">
         <f t="shared" si="5"/>
         <v>1.5501730103806288E-2</v>
       </c>
@@ -12140,13 +12157,13 @@
       </c>
     </row>
     <row r="172" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A172" s="25">
+      <c r="A172" s="23">
         <v>39171</v>
       </c>
       <c r="B172">
         <v>4.4578999999999898</v>
       </c>
-      <c r="C172" s="27">
+      <c r="C172" s="25">
         <f t="shared" si="5"/>
         <v>1.2652764526827509E-2</v>
       </c>
@@ -12156,13 +12173,13 @@
       </c>
     </row>
     <row r="173" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A173" s="25">
+      <c r="A173" s="23">
         <v>39202</v>
       </c>
       <c r="B173">
         <v>4.5254999999999903</v>
       </c>
-      <c r="C173" s="27">
+      <c r="C173" s="25">
         <f t="shared" si="5"/>
         <v>1.5164090715359402E-2</v>
       </c>
@@ -12172,13 +12189,13 @@
       </c>
     </row>
     <row r="174" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A174" s="25">
+      <c r="A174" s="23">
         <v>39233</v>
       </c>
       <c r="B174">
         <v>4.6720999999999897</v>
       </c>
-      <c r="C174" s="27">
+      <c r="C174" s="25">
         <f t="shared" si="5"/>
         <v>3.2394210584465677E-2</v>
       </c>
@@ -12188,13 +12205,13 @@
       </c>
     </row>
     <row r="175" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A175" s="25">
+      <c r="A175" s="23">
         <v>39262</v>
       </c>
       <c r="B175">
         <v>4.7060999999999904</v>
       </c>
-      <c r="C175" s="27">
+      <c r="C175" s="25">
         <f t="shared" si="5"/>
         <v>7.2772414973996113E-3</v>
       </c>
@@ -12204,13 +12221,13 @@
       </c>
     </row>
     <row r="176" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A176" s="25">
+      <c r="A176" s="23">
         <v>39294</v>
       </c>
       <c r="B176">
         <v>4.7515999999999901</v>
       </c>
-      <c r="C176" s="27">
+      <c r="C176" s="25">
         <f t="shared" si="5"/>
         <v>9.6683028409936256E-3</v>
       </c>
@@ -12220,13 +12237,13 @@
       </c>
     </row>
     <row r="177" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A177" s="25">
+      <c r="A177" s="23">
         <v>39325</v>
       </c>
       <c r="B177">
         <v>4.6623999999999901</v>
       </c>
-      <c r="C177" s="27">
+      <c r="C177" s="25">
         <f t="shared" si="5"/>
         <v>-1.8772623958245638E-2</v>
       </c>
@@ -12236,13 +12253,13 @@
       </c>
     </row>
     <row r="178" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A178" s="25">
+      <c r="A178" s="23">
         <v>39353</v>
       </c>
       <c r="B178">
         <v>4.7369999999999903</v>
       </c>
-      <c r="C178" s="27">
+      <c r="C178" s="25">
         <f t="shared" si="5"/>
         <v>1.6000343170899267E-2</v>
       </c>
@@ -12252,13 +12269,13 @@
       </c>
     </row>
     <row r="179" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A179" s="25">
+      <c r="A179" s="23">
         <v>39386</v>
       </c>
       <c r="B179">
         <v>4.87469999999999</v>
       </c>
-      <c r="C179" s="27">
+      <c r="C179" s="25">
         <f t="shared" si="5"/>
         <v>2.9069031032298964E-2</v>
       </c>
@@ -12268,13 +12285,13 @@
       </c>
     </row>
     <row r="180" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A180" s="25">
+      <c r="A180" s="23">
         <v>39416</v>
       </c>
       <c r="B180">
         <v>4.7928999999999897</v>
       </c>
-      <c r="C180" s="27">
+      <c r="C180" s="25">
         <f t="shared" si="5"/>
         <v>-1.678051982686124E-2</v>
       </c>
@@ -12284,13 +12301,13 @@
       </c>
     </row>
     <row r="181" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A181" s="25">
+      <c r="A181" s="23">
         <v>39447</v>
       </c>
       <c r="B181">
         <v>4.8079999999999901</v>
       </c>
-      <c r="C181" s="27">
+      <c r="C181" s="25">
         <f t="shared" si="5"/>
         <v>3.1504934382107219E-3</v>
       </c>
@@ -12300,13 +12317,13 @@
       </c>
     </row>
     <row r="182" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A182" s="25">
+      <c r="A182" s="23">
         <v>39478</v>
       </c>
       <c r="B182">
         <v>4.6905999999999901</v>
       </c>
-      <c r="C182" s="27">
+      <c r="C182" s="25">
         <f t="shared" si="5"/>
         <v>-2.4417637271214709E-2</v>
       </c>
@@ -12316,13 +12333,13 @@
       </c>
     </row>
     <row r="183" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A183" s="25">
+      <c r="A183" s="23">
         <v>39507</v>
       </c>
       <c r="B183">
         <v>4.73029999999999</v>
       </c>
-      <c r="C183" s="27">
+      <c r="C183" s="25">
         <f t="shared" si="5"/>
         <v>8.4637359826034153E-3</v>
       </c>
@@ -12332,13 +12349,13 @@
       </c>
     </row>
     <row r="184" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A184" s="25">
+      <c r="A184" s="23">
         <v>39538</v>
       </c>
       <c r="B184">
         <v>4.64909999999999</v>
       </c>
-      <c r="C184" s="27">
+      <c r="C184" s="25">
         <f t="shared" si="5"/>
         <v>-1.7165930279263497E-2</v>
       </c>
@@ -12348,13 +12365,13 @@
       </c>
     </row>
     <row r="185" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A185" s="25">
+      <c r="A185" s="23">
         <v>39568</v>
       </c>
       <c r="B185">
         <v>4.6727999999999899</v>
       </c>
-      <c r="C185" s="27">
+      <c r="C185" s="25">
         <f t="shared" si="5"/>
         <v>5.0977608569400257E-3</v>
       </c>
@@ -12364,13 +12381,13 @@
       </c>
     </row>
     <row r="186" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A186" s="25">
+      <c r="A186" s="23">
         <v>39598</v>
       </c>
       <c r="B186">
         <v>4.7611999999999899</v>
       </c>
-      <c r="C186" s="27">
+      <c r="C186" s="25">
         <f t="shared" si="5"/>
         <v>1.8917993494264707E-2</v>
       </c>
@@ -12380,13 +12397,13 @@
       </c>
     </row>
     <row r="187" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A187" s="25">
+      <c r="A187" s="23">
         <v>39629</v>
       </c>
       <c r="B187">
         <v>4.7539999999999898</v>
       </c>
-      <c r="C187" s="27">
+      <c r="C187" s="25">
         <f t="shared" si="5"/>
         <v>-1.5122238091237472E-3</v>
       </c>
@@ -12396,13 +12413,13 @@
       </c>
     </row>
     <row r="188" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A188" s="25">
+      <c r="A188" s="23">
         <v>39660</v>
       </c>
       <c r="B188">
         <v>4.6335999999999897</v>
       </c>
-      <c r="C188" s="27">
+      <c r="C188" s="25">
         <f t="shared" si="5"/>
         <v>-2.5326041228439289E-2</v>
       </c>
@@ -12412,13 +12429,13 @@
       </c>
     </row>
     <row r="189" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A189" s="25">
+      <c r="A189" s="23">
         <v>39689</v>
       </c>
       <c r="B189">
         <v>4.6263999999999896</v>
       </c>
-      <c r="C189" s="27">
+      <c r="C189" s="25">
         <f t="shared" si="5"/>
         <v>-1.5538674033149791E-3</v>
       </c>
@@ -12428,13 +12445,13 @@
       </c>
     </row>
     <row r="190" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A190" s="25">
+      <c r="A190" s="23">
         <v>39721</v>
       </c>
       <c r="B190">
         <v>4.3602999999999899</v>
       </c>
-      <c r="C190" s="27">
+      <c r="C190" s="25">
         <f t="shared" si="5"/>
         <v>-5.7517724364516742E-2</v>
       </c>
@@ -12444,13 +12461,13 @@
       </c>
     </row>
     <row r="191" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A191" s="25">
+      <c r="A191" s="23">
         <v>39752</v>
       </c>
       <c r="B191">
         <v>4.1384999999999899</v>
       </c>
-      <c r="C191" s="27">
+      <c r="C191" s="25">
         <f t="shared" si="5"/>
         <v>-5.0868059537187871E-2</v>
       </c>
@@ -12460,13 +12477,13 @@
       </c>
     </row>
     <row r="192" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A192" s="25">
+      <c r="A192" s="23">
         <v>39780</v>
       </c>
       <c r="B192">
         <v>4.0055999999999896</v>
       </c>
-      <c r="C192" s="27">
+      <c r="C192" s="25">
         <f t="shared" si="5"/>
         <v>-3.2113084450888119E-2</v>
       </c>
@@ -12476,13 +12493,13 @@
       </c>
     </row>
     <row r="193" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A193" s="25">
+      <c r="A193" s="23">
         <v>39813</v>
       </c>
       <c r="B193">
         <v>3.9551999999999898</v>
       </c>
-      <c r="C193" s="27">
+      <c r="C193" s="25">
         <f t="shared" si="5"/>
         <v>-1.2582384661473878E-2</v>
       </c>
@@ -12492,13 +12509,13 @@
       </c>
     </row>
     <row r="194" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A194" s="25">
+      <c r="A194" s="23">
         <v>39843</v>
       </c>
       <c r="B194">
         <v>3.98639999999999</v>
       </c>
-      <c r="C194" s="27">
+      <c r="C194" s="25">
         <f t="shared" si="5"/>
         <v>7.8883495145631866E-3</v>
       </c>
@@ -12508,13 +12525,13 @@
       </c>
     </row>
     <row r="195" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A195" s="25">
+      <c r="A195" s="23">
         <v>39871</v>
       </c>
       <c r="B195">
         <v>3.94119999999999</v>
       </c>
-      <c r="C195" s="27">
+      <c r="C195" s="25">
         <f t="shared" si="5"/>
         <v>-1.1338551073650449E-2</v>
       </c>
@@ -12524,13 +12541,13 @@
       </c>
     </row>
     <row r="196" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A196" s="25">
+      <c r="A196" s="23">
         <v>39903</v>
       </c>
       <c r="B196">
         <v>3.9475999999999898</v>
       </c>
-      <c r="C196" s="27">
+      <c r="C196" s="25">
         <f t="shared" si="5"/>
         <v>1.6238709022631248E-3</v>
       </c>
@@ -12540,13 +12557,13 @@
       </c>
     </row>
     <row r="197" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A197" s="25">
+      <c r="A197" s="23">
         <v>39933</v>
       </c>
       <c r="B197">
         <v>4.0059999999999896</v>
       </c>
-      <c r="C197" s="27">
+      <c r="C197" s="25">
         <f t="shared" si="5"/>
         <v>1.4793798763805821E-2</v>
       </c>
@@ -12556,13 +12573,13 @@
       </c>
     </row>
     <row r="198" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A198" s="25">
+      <c r="A198" s="23">
         <v>39962</v>
       </c>
       <c r="B198">
         <v>4.1749999999999901</v>
       </c>
-      <c r="C198" s="27">
+      <c r="C198" s="25">
         <f t="shared" si="5"/>
         <v>4.2186719920120019E-2</v>
       </c>
@@ -12572,13 +12589,13 @@
       </c>
     </row>
     <row r="199" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A199" s="25">
+      <c r="A199" s="23">
         <v>39994</v>
       </c>
       <c r="B199">
         <v>4.2173999999999898</v>
       </c>
-      <c r="C199" s="27">
+      <c r="C199" s="25">
         <f t="shared" si="5"/>
         <v>1.0155688622754511E-2</v>
       </c>
@@ -12588,13 +12605,13 @@
       </c>
     </row>
     <row r="200" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A200" s="25">
+      <c r="A200" s="23">
         <v>40025</v>
       </c>
       <c r="B200">
         <v>4.3155999999999901</v>
       </c>
-      <c r="C200" s="27">
+      <c r="C200" s="25">
         <f t="shared" si="5"/>
         <v>2.3284488073220588E-2</v>
       </c>
@@ -12604,13 +12621,13 @@
       </c>
     </row>
     <row r="201" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A201" s="25">
+      <c r="A201" s="23">
         <v>40056</v>
       </c>
       <c r="B201">
         <v>4.4092999999999902</v>
       </c>
-      <c r="C201" s="27">
+      <c r="C201" s="25">
         <f t="shared" si="5"/>
         <v>2.1711928816387172E-2</v>
       </c>
@@ -12620,13 +12637,13 @@
       </c>
     </row>
     <row r="202" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A202" s="25">
+      <c r="A202" s="23">
         <v>40086</v>
       </c>
       <c r="B202">
         <v>4.5368999999999904</v>
       </c>
-      <c r="C202" s="27">
+      <c r="C202" s="25">
         <f t="shared" si="5"/>
         <v>2.8938833828499044E-2</v>
       </c>
@@ -12636,13 +12653,13 @@
       </c>
     </row>
     <row r="203" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A203" s="25">
+      <c r="A203" s="23">
         <v>40116</v>
       </c>
       <c r="B203">
         <v>4.55649999999999</v>
       </c>
-      <c r="C203" s="27">
+      <c r="C203" s="25">
         <f t="shared" si="5"/>
         <v>4.320130485573781E-3</v>
       </c>
@@ -12652,13 +12669,13 @@
       </c>
     </row>
     <row r="204" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A204" s="25">
+      <c r="A204" s="23">
         <v>40147</v>
       </c>
       <c r="B204">
         <v>4.6550999999999902</v>
       </c>
-      <c r="C204" s="27">
+      <c r="C204" s="25">
         <f t="shared" si="5"/>
         <v>2.1639416218588892E-2</v>
       </c>
@@ -12668,13 +12685,13 @@
       </c>
     </row>
     <row r="205" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A205" s="25">
+      <c r="A205" s="23">
         <v>40178</v>
       </c>
       <c r="B205">
         <v>4.7612999999999897</v>
       </c>
-      <c r="C205" s="27">
+      <c r="C205" s="25">
         <f t="shared" si="5"/>
         <v>2.281368821292773E-2</v>
       </c>
@@ -12684,13 +12701,13 @@
       </c>
     </row>
     <row r="206" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A206" s="25">
+      <c r="A206" s="23">
         <v>40207</v>
       </c>
       <c r="B206">
         <v>4.8287999999999904</v>
       </c>
-      <c r="C206" s="27">
+      <c r="C206" s="25">
         <f t="shared" si="5"/>
         <v>1.4176800453657767E-2</v>
       </c>
@@ -12700,13 +12717,13 @@
       </c>
     </row>
     <row r="207" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A207" s="25">
+      <c r="A207" s="23">
         <v>40235</v>
       </c>
       <c r="B207">
         <v>4.8498999999999901</v>
       </c>
-      <c r="C207" s="27">
+      <c r="C207" s="25">
         <f t="shared" ref="C207:C270" si="7">B207/B206-1</f>
         <v>4.3696156394963381E-3</v>
       </c>
@@ -12716,13 +12733,13 @@
       </c>
     </row>
     <row r="208" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A208" s="25">
+      <c r="A208" s="23">
         <v>40268</v>
       </c>
       <c r="B208">
         <v>4.9880999999999904</v>
       </c>
-      <c r="C208" s="27">
+      <c r="C208" s="25">
         <f t="shared" si="7"/>
         <v>2.8495432895523809E-2</v>
       </c>
@@ -12732,13 +12749,13 @@
       </c>
     </row>
     <row r="209" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A209" s="25">
+      <c r="A209" s="23">
         <v>40298</v>
       </c>
       <c r="B209">
         <v>5.08239999999999</v>
       </c>
-      <c r="C209" s="27">
+      <c r="C209" s="25">
         <f t="shared" si="7"/>
         <v>1.8904993885447308E-2</v>
       </c>
@@ -12748,13 +12765,13 @@
       </c>
     </row>
     <row r="210" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A210" s="25">
+      <c r="A210" s="23">
         <v>40329</v>
       </c>
       <c r="B210">
         <v>4.9262999999999897</v>
       </c>
-      <c r="C210" s="27">
+      <c r="C210" s="25">
         <f t="shared" si="7"/>
         <v>-3.0713835983000259E-2</v>
       </c>
@@ -12764,13 +12781,13 @@
       </c>
     </row>
     <row r="211" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A211" s="25">
+      <c r="A211" s="23">
         <v>40359</v>
       </c>
       <c r="B211">
         <v>4.8486999999999902</v>
       </c>
-      <c r="C211" s="27">
+      <c r="C211" s="25">
         <f t="shared" si="7"/>
         <v>-1.5752187239916338E-2</v>
       </c>
@@ -12780,13 +12797,13 @@
       </c>
     </row>
     <row r="212" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A212" s="25">
+      <c r="A212" s="23">
         <v>40389</v>
       </c>
       <c r="B212">
         <v>4.9243999999999897</v>
       </c>
-      <c r="C212" s="27">
+      <c r="C212" s="25">
         <f t="shared" si="7"/>
         <v>1.5612432198321091E-2</v>
       </c>
@@ -12796,13 +12813,13 @@
       </c>
     </row>
     <row r="213" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A213" s="25">
+      <c r="A213" s="23">
         <v>40421</v>
       </c>
       <c r="B213">
         <v>4.9045999999999896</v>
       </c>
-      <c r="C213" s="27">
+      <c r="C213" s="25">
         <f t="shared" si="7"/>
         <v>-4.0207944115019378E-3</v>
       </c>
@@ -12812,13 +12829,13 @@
       </c>
     </row>
     <row r="214" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A214" s="25">
+      <c r="A214" s="23">
         <v>40451</v>
       </c>
       <c r="B214">
         <v>5.0615999999999897</v>
       </c>
-      <c r="C214" s="27">
+      <c r="C214" s="25">
         <f t="shared" si="7"/>
         <v>3.2010765403906571E-2</v>
       </c>
@@ -12828,13 +12845,13 @@
       </c>
     </row>
     <row r="215" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A215" s="25">
+      <c r="A215" s="23">
         <v>40480</v>
       </c>
       <c r="B215">
         <v>5.1524999999999901</v>
       </c>
-      <c r="C215" s="27">
+      <c r="C215" s="25">
         <f t="shared" si="7"/>
         <v>1.7958748221906129E-2</v>
       </c>
@@ -12844,13 +12861,13 @@
       </c>
     </row>
     <row r="216" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A216" s="25">
+      <c r="A216" s="23">
         <v>40512</v>
       </c>
       <c r="B216">
         <v>5.1599999999999904</v>
       </c>
-      <c r="C216" s="27">
+      <c r="C216" s="25">
         <f t="shared" si="7"/>
         <v>1.4556040756914523E-3</v>
       </c>
@@ -12860,13 +12877,13 @@
       </c>
     </row>
     <row r="217" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A217" s="25">
+      <c r="A217" s="23">
         <v>40543</v>
       </c>
       <c r="B217">
         <v>5.3625999999999898</v>
       </c>
-      <c r="C217" s="27">
+      <c r="C217" s="25">
         <f t="shared" si="7"/>
         <v>3.926356589147284E-2</v>
       </c>
@@ -12876,13 +12893,13 @@
       </c>
     </row>
     <row r="218" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A218" s="25">
+      <c r="A218" s="23">
         <v>40574</v>
       </c>
       <c r="B218">
         <v>5.45929999999999</v>
       </c>
-      <c r="C218" s="27">
+      <c r="C218" s="25">
         <f t="shared" si="7"/>
         <v>1.8032297766009009E-2</v>
       </c>
@@ -12892,13 +12909,13 @@
       </c>
     </row>
     <row r="219" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A219" s="25">
+      <c r="A219" s="23">
         <v>40602</v>
       </c>
       <c r="B219">
         <v>5.5380999999999903</v>
       </c>
-      <c r="C219" s="27">
+      <c r="C219" s="25">
         <f t="shared" si="7"/>
         <v>1.443408495594678E-2</v>
       </c>
@@ -12908,13 +12925,13 @@
       </c>
     </row>
     <row r="220" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A220" s="25">
+      <c r="A220" s="23">
         <v>40633</v>
       </c>
       <c r="B220">
         <v>5.5237999999999898</v>
       </c>
-      <c r="C220" s="27">
+      <c r="C220" s="25">
         <f t="shared" si="7"/>
         <v>-2.5821129990430958E-3</v>
       </c>
@@ -12924,13 +12941,13 @@
       </c>
     </row>
     <row r="221" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A221" s="25">
+      <c r="A221" s="23">
         <v>40662</v>
       </c>
       <c r="B221">
         <v>5.5866999999999898</v>
       </c>
-      <c r="C221" s="27">
+      <c r="C221" s="25">
         <f t="shared" si="7"/>
         <v>1.138708859842863E-2</v>
       </c>
@@ -12940,13 +12957,13 @@
       </c>
     </row>
     <row r="222" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A222" s="25">
+      <c r="A222" s="23">
         <v>40694</v>
       </c>
       <c r="B222">
         <v>5.5527999999999897</v>
       </c>
-      <c r="C222" s="27">
+      <c r="C222" s="25">
         <f t="shared" si="7"/>
         <v>-6.0679828879303122E-3</v>
       </c>
@@ -12956,13 +12973,13 @@
       </c>
     </row>
     <row r="223" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A223" s="25">
+      <c r="A223" s="23">
         <v>40724</v>
       </c>
       <c r="B223">
         <v>5.4328999999999903</v>
       </c>
-      <c r="C223" s="27">
+      <c r="C223" s="25">
         <f t="shared" si="7"/>
         <v>-2.1592709984152081E-2</v>
       </c>
@@ -12972,13 +12989,13 @@
       </c>
     </row>
     <row r="224" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A224" s="25">
+      <c r="A224" s="23">
         <v>40753</v>
       </c>
       <c r="B224">
         <v>5.3906999999999901</v>
       </c>
-      <c r="C224" s="27">
+      <c r="C224" s="25">
         <f t="shared" si="7"/>
         <v>-7.7674906587642534E-3</v>
       </c>
@@ -12988,13 +13005,13 @@
       </c>
     </row>
     <row r="225" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A225" s="25">
+      <c r="A225" s="23">
         <v>40786</v>
       </c>
       <c r="B225">
         <v>5.1012999999999904</v>
       </c>
-      <c r="C225" s="27">
+      <c r="C225" s="25">
         <f t="shared" si="7"/>
         <v>-5.3685050179012039E-2</v>
       </c>
@@ -13004,13 +13021,13 @@
       </c>
     </row>
     <row r="226" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A226" s="25">
+      <c r="A226" s="23">
         <v>40816</v>
       </c>
       <c r="B226">
         <v>4.84309999999999</v>
       </c>
-      <c r="C226" s="27">
+      <c r="C226" s="25">
         <f t="shared" si="7"/>
         <v>-5.0614549232548711E-2</v>
       </c>
@@ -13020,13 +13037,13 @@
       </c>
     </row>
     <row r="227" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A227" s="25">
+      <c r="A227" s="23">
         <v>40847</v>
       </c>
       <c r="B227">
         <v>4.9669999999999899</v>
       </c>
-      <c r="C227" s="27">
+      <c r="C227" s="25">
         <f t="shared" si="7"/>
         <v>2.5582787883793534E-2</v>
       </c>
@@ -13036,13 +13053,13 @@
       </c>
     </row>
     <row r="228" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A228" s="25">
+      <c r="A228" s="23">
         <v>40877</v>
       </c>
       <c r="B228">
         <v>4.9147999999999898</v>
       </c>
-      <c r="C228" s="27">
+      <c r="C228" s="25">
         <f t="shared" si="7"/>
         <v>-1.0509361787799487E-2</v>
       </c>
@@ -13052,13 +13069,13 @@
       </c>
     </row>
     <row r="229" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A229" s="25">
+      <c r="A229" s="23">
         <v>40907</v>
       </c>
       <c r="B229">
         <v>4.8751999999999898</v>
       </c>
-      <c r="C229" s="27">
+      <c r="C229" s="25">
         <f t="shared" si="7"/>
         <v>-8.0572963294539557E-3</v>
       </c>
@@ -13068,13 +13085,13 @@
       </c>
     </row>
     <row r="230" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A230" s="25">
+      <c r="A230" s="23">
         <v>40939</v>
       </c>
       <c r="B230">
         <v>5.01189999999999</v>
       </c>
-      <c r="C230" s="27">
+      <c r="C230" s="25">
         <f t="shared" si="7"/>
         <v>2.8039875287167781E-2</v>
       </c>
@@ -13084,13 +13101,13 @@
       </c>
     </row>
     <row r="231" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A231" s="25">
+      <c r="A231" s="23">
         <v>40968</v>
       </c>
       <c r="B231">
         <v>5.09119999999999</v>
       </c>
-      <c r="C231" s="27">
+      <c r="C231" s="25">
         <f t="shared" si="7"/>
         <v>1.5822342824078683E-2</v>
       </c>
@@ -13100,13 +13117,13 @@
       </c>
     </row>
     <row r="232" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A232" s="25">
+      <c r="A232" s="23">
         <v>40998</v>
       </c>
       <c r="B232">
         <v>5.1312999999999898</v>
       </c>
-      <c r="C232" s="27">
+      <c r="C232" s="25">
         <f t="shared" si="7"/>
         <v>7.8763356379634164E-3</v>
       </c>
@@ -13116,13 +13133,13 @@
       </c>
     </row>
     <row r="233" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A233" s="25">
+      <c r="A233" s="23">
         <v>41029</v>
       </c>
       <c r="B233">
         <v>5.1196999999999901</v>
       </c>
-      <c r="C233" s="27">
+      <c r="C233" s="25">
         <f t="shared" si="7"/>
         <v>-2.2606357063511551E-3</v>
       </c>
@@ -13132,13 +13149,13 @@
       </c>
     </row>
     <row r="234" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A234" s="25">
+      <c r="A234" s="23">
         <v>41060</v>
       </c>
       <c r="B234">
         <v>5.0518999999999901</v>
       </c>
-      <c r="C234" s="27">
+      <c r="C234" s="25">
         <f t="shared" si="7"/>
         <v>-1.3242963454889956E-2</v>
       </c>
@@ -13148,13 +13165,13 @@
       </c>
     </row>
     <row r="235" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A235" s="25">
+      <c r="A235" s="23">
         <v>41089</v>
       </c>
       <c r="B235">
         <v>5.04279999999999</v>
       </c>
-      <c r="C235" s="27">
+      <c r="C235" s="25">
         <f t="shared" si="7"/>
         <v>-1.8013024802550071E-3</v>
       </c>
@@ -13164,13 +13181,13 @@
       </c>
     </row>
     <row r="236" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A236" s="25">
+      <c r="A236" s="23">
         <v>41121</v>
       </c>
       <c r="B236">
         <v>5.0802999999999896</v>
       </c>
-      <c r="C236" s="27">
+      <c r="C236" s="25">
         <f t="shared" si="7"/>
         <v>7.4363448877607929E-3</v>
       </c>
@@ -13180,13 +13197,13 @@
       </c>
     </row>
     <row r="237" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A237" s="25">
+      <c r="A237" s="23">
         <v>41152</v>
       </c>
       <c r="B237">
         <v>5.1400999999999897</v>
       </c>
-      <c r="C237" s="27">
+      <c r="C237" s="25">
         <f t="shared" si="7"/>
         <v>1.1770958407968157E-2</v>
       </c>
@@ -13196,13 +13213,13 @@
       </c>
     </row>
     <row r="238" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A238" s="25">
+      <c r="A238" s="23">
         <v>41180</v>
       </c>
       <c r="B238">
         <v>5.22569999999999</v>
       </c>
-      <c r="C238" s="27">
+      <c r="C238" s="25">
         <f t="shared" si="7"/>
         <v>1.6653372502480668E-2</v>
       </c>
@@ -13212,13 +13229,13 @@
       </c>
     </row>
     <row r="239" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A239" s="25">
+      <c r="A239" s="23">
         <v>41213</v>
       </c>
       <c r="B239">
         <v>5.2734999999999896</v>
       </c>
-      <c r="C239" s="27">
+      <c r="C239" s="25">
         <f t="shared" si="7"/>
         <v>9.1470999100597972E-3</v>
       </c>
@@ -13228,13 +13245,13 @@
       </c>
     </row>
     <row r="240" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A240" s="25">
+      <c r="A240" s="23">
         <v>41243</v>
       </c>
       <c r="B240">
         <v>5.2890999999999897</v>
       </c>
-      <c r="C240" s="27">
+      <c r="C240" s="25">
         <f t="shared" si="7"/>
         <v>2.9581871622261779E-3</v>
       </c>
@@ -13244,13 +13261,13 @@
       </c>
     </row>
     <row r="241" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A241" s="25">
+      <c r="A241" s="23">
         <v>41274</v>
       </c>
       <c r="B241">
         <v>5.3935999999999904</v>
       </c>
-      <c r="C241" s="27">
+      <c r="C241" s="25">
         <f t="shared" si="7"/>
         <v>1.9757614717059724E-2</v>
       </c>
@@ -13260,13 +13277,13 @@
       </c>
     </row>
     <row r="242" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A242" s="25">
+      <c r="A242" s="23">
         <v>41305</v>
       </c>
       <c r="B242">
         <v>5.5094999999999903</v>
       </c>
-      <c r="C242" s="27">
+      <c r="C242" s="25">
         <f t="shared" si="7"/>
         <v>2.1488430732720332E-2</v>
       </c>
@@ -13276,13 +13293,13 @@
       </c>
     </row>
     <row r="243" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A243" s="25">
+      <c r="A243" s="23">
         <v>41333</v>
       </c>
       <c r="B243">
         <v>5.5345999999999904</v>
       </c>
-      <c r="C243" s="27">
+      <c r="C243" s="25">
         <f t="shared" si="7"/>
         <v>4.5557673110083741E-3</v>
       </c>
@@ -13292,13 +13309,13 @@
       </c>
     </row>
     <row r="244" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A244" s="25">
+      <c r="A244" s="23">
         <v>41362</v>
       </c>
       <c r="B244">
         <v>5.6512999999999902</v>
       </c>
-      <c r="C244" s="27">
+      <c r="C244" s="25">
         <f t="shared" si="7"/>
         <v>2.1085534636649417E-2</v>
       </c>
@@ -13308,13 +13325,13 @@
       </c>
     </row>
     <row r="245" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A245" s="25">
+      <c r="A245" s="23">
         <v>41394</v>
       </c>
       <c r="B245">
         <v>5.7188999999999899</v>
       </c>
-      <c r="C245" s="27">
+      <c r="C245" s="25">
         <f t="shared" si="7"/>
         <v>1.196184948595902E-2</v>
       </c>
@@ -13324,13 +13341,13 @@
       </c>
     </row>
     <row r="246" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A246" s="25">
+      <c r="A246" s="23">
         <v>41425</v>
       </c>
       <c r="B246">
         <v>5.8489999999999798</v>
       </c>
-      <c r="C246" s="27">
+      <c r="C246" s="25">
         <f t="shared" si="7"/>
         <v>2.2749130077460711E-2</v>
       </c>
@@ -13340,13 +13357,13 @@
       </c>
     </row>
     <row r="247" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A247" s="25">
+      <c r="A247" s="23">
         <v>41453</v>
       </c>
       <c r="B247">
         <v>5.7722999999999898</v>
       </c>
-      <c r="C247" s="27">
+      <c r="C247" s="25">
         <f t="shared" si="7"/>
         <v>-1.3113352709863246E-2</v>
       </c>
@@ -13356,13 +13373,13 @@
       </c>
     </row>
     <row r="248" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A248" s="25">
+      <c r="A248" s="23">
         <v>41486</v>
       </c>
       <c r="B248">
         <v>5.8596999999999797</v>
       </c>
-      <c r="C248" s="27">
+      <c r="C248" s="25">
         <f t="shared" si="7"/>
         <v>1.514127817334332E-2</v>
       </c>
@@ -13372,13 +13389,13 @@
       </c>
     </row>
     <row r="249" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A249" s="25">
+      <c r="A249" s="23">
         <v>41516</v>
       </c>
       <c r="B249">
         <v>5.8571999999999802</v>
       </c>
-      <c r="C249" s="27">
+      <c r="C249" s="25">
         <f t="shared" si="7"/>
         <v>-4.2664300220141005E-4</v>
       </c>
@@ -13388,13 +13405,13 @@
       </c>
     </row>
     <row r="250" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A250" s="25">
+      <c r="A250" s="23">
         <v>41547</v>
       </c>
       <c r="B250">
         <v>5.9421999999999802</v>
       </c>
-      <c r="C250" s="27">
+      <c r="C250" s="25">
         <f t="shared" si="7"/>
         <v>1.4512053540941094E-2</v>
       </c>
@@ -13404,13 +13421,13 @@
       </c>
     </row>
     <row r="251" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A251" s="25">
+      <c r="A251" s="23">
         <v>41578</v>
       </c>
       <c r="B251">
         <v>6.0280999999999798</v>
       </c>
-      <c r="C251" s="27">
+      <c r="C251" s="25">
         <f t="shared" si="7"/>
         <v>1.445592541482954E-2</v>
       </c>
@@ -13420,13 +13437,13 @@
       </c>
     </row>
     <row r="252" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A252" s="25">
+      <c r="A252" s="23">
         <v>41607</v>
       </c>
       <c r="B252">
         <v>6.1291999999999804</v>
       </c>
-      <c r="C252" s="27">
+      <c r="C252" s="25">
         <f t="shared" si="7"/>
         <v>1.6771453691876603E-2</v>
       </c>
@@ -13436,13 +13453,13 @@
       </c>
     </row>
     <row r="253" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A253" s="25">
+      <c r="A253" s="23">
         <v>41639</v>
       </c>
       <c r="B253">
         <v>6.2277999999999798</v>
       </c>
-      <c r="C253" s="27">
+      <c r="C253" s="25">
         <f t="shared" si="7"/>
         <v>1.6086928147229562E-2</v>
       </c>
@@ -13452,13 +13469,13 @@
       </c>
     </row>
     <row r="254" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A254" s="25">
+      <c r="A254" s="23">
         <v>41670</v>
       </c>
       <c r="B254">
         <v>6.2456999999999798</v>
       </c>
-      <c r="C254" s="27">
+      <c r="C254" s="25">
         <f t="shared" si="7"/>
         <v>2.8742091910465284E-3</v>
       </c>
@@ -13468,13 +13485,13 @@
       </c>
     </row>
     <row r="255" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A255" s="25">
+      <c r="A255" s="23">
         <v>41698</v>
       </c>
       <c r="B255">
         <v>6.4171999999999798</v>
       </c>
-      <c r="C255" s="27">
+      <c r="C255" s="25">
         <f t="shared" si="7"/>
         <v>2.7458891717501821E-2</v>
       </c>
@@ -13484,13 +13501,13 @@
       </c>
     </row>
     <row r="256" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A256" s="25">
+      <c r="A256" s="23">
         <v>41729</v>
       </c>
       <c r="B256">
         <v>6.4081999999999804</v>
       </c>
-      <c r="C256" s="27">
+      <c r="C256" s="25">
         <f t="shared" si="7"/>
         <v>-1.4024808327618432E-3</v>
       </c>
@@ -13500,13 +13517,13 @@
       </c>
     </row>
     <row r="257" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A257" s="25">
+      <c r="A257" s="23">
         <v>41759</v>
       </c>
       <c r="B257">
         <v>6.4099999999999797</v>
       </c>
-      <c r="C257" s="27">
+      <c r="C257" s="25">
         <f t="shared" si="7"/>
         <v>2.8089010954701621E-4</v>
       </c>
@@ -13516,13 +13533,13 @@
       </c>
     </row>
     <row r="258" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A258" s="25">
+      <c r="A258" s="23">
         <v>41789</v>
       </c>
       <c r="B258">
         <v>6.4783999999999802</v>
       </c>
-      <c r="C258" s="27">
+      <c r="C258" s="25">
         <f t="shared" si="7"/>
         <v>1.0670826833073521E-2</v>
       </c>
@@ -13532,13 +13549,13 @@
       </c>
     </row>
     <row r="259" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A259" s="25">
+      <c r="A259" s="23">
         <v>41820</v>
       </c>
       <c r="B259">
         <v>6.5858999999999801</v>
       </c>
-      <c r="C259" s="27">
+      <c r="C259" s="25">
         <f t="shared" si="7"/>
         <v>1.659360335885407E-2</v>
       </c>
@@ -13548,13 +13565,13 @@
       </c>
     </row>
     <row r="260" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A260" s="25">
+      <c r="A260" s="23">
         <v>41851</v>
       </c>
       <c r="B260">
         <v>6.5467999999999797</v>
       </c>
-      <c r="C260" s="27">
+      <c r="C260" s="25">
         <f t="shared" si="7"/>
         <v>-5.936925856754649E-3</v>
       </c>
@@ -13564,13 +13581,13 @@
       </c>
     </row>
     <row r="261" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A261" s="25">
+      <c r="A261" s="23">
         <v>41880</v>
       </c>
       <c r="B261">
         <v>6.55469999999998</v>
       </c>
-      <c r="C261" s="27">
+      <c r="C261" s="25">
         <f t="shared" si="7"/>
         <v>1.2066964012953374E-3</v>
       </c>
@@ -13580,13 +13597,13 @@
       </c>
     </row>
     <row r="262" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A262" s="25">
+      <c r="A262" s="23">
         <v>41912</v>
       </c>
       <c r="B262">
         <v>6.4650999999999801</v>
       </c>
-      <c r="C262" s="27">
+      <c r="C262" s="25">
         <f t="shared" si="7"/>
         <v>-1.3669580606282539E-2</v>
       </c>
@@ -13596,13 +13613,13 @@
       </c>
     </row>
     <row r="263" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A263" s="25">
+      <c r="A263" s="23">
         <v>41943</v>
       </c>
       <c r="B263">
         <v>6.3252999999999799</v>
       </c>
-      <c r="C263" s="27">
+      <c r="C263" s="25">
         <f t="shared" si="7"/>
         <v>-2.1623795455600114E-2</v>
       </c>
@@ -13612,13 +13629,13 @@
       </c>
     </row>
     <row r="264" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A264" s="25">
+      <c r="A264" s="23">
         <v>41971</v>
       </c>
       <c r="B264">
         <v>6.3603999999999798</v>
       </c>
-      <c r="C264" s="27">
+      <c r="C264" s="25">
         <f t="shared" si="7"/>
         <v>5.5491439141226451E-3</v>
       </c>
@@ -13628,13 +13645,13 @@
       </c>
     </row>
     <row r="265" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A265" s="25">
+      <c r="A265" s="23">
         <v>42004</v>
       </c>
       <c r="B265">
         <v>6.3256999999999799</v>
       </c>
-      <c r="C265" s="27">
+      <c r="C265" s="25">
         <f t="shared" si="7"/>
         <v>-5.4556317212753891E-3</v>
       </c>
@@ -13644,13 +13661,13 @@
       </c>
     </row>
     <row r="266" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A266" s="25">
+      <c r="A266" s="23">
         <v>42034</v>
       </c>
       <c r="B266">
         <v>6.2621999999999796</v>
       </c>
-      <c r="C266" s="27">
+      <c r="C266" s="25">
         <f t="shared" si="7"/>
         <v>-1.0038414720900501E-2</v>
       </c>
@@ -13660,13 +13677,13 @@
       </c>
     </row>
     <row r="267" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A267" s="25">
+      <c r="A267" s="23">
         <v>42062</v>
       </c>
       <c r="B267">
         <v>6.4027999999999796</v>
       </c>
-      <c r="C267" s="27">
+      <c r="C267" s="25">
         <f t="shared" si="7"/>
         <v>2.2452173357605965E-2</v>
       </c>
@@ -13676,13 +13693,13 @@
       </c>
     </row>
     <row r="268" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A268" s="25">
+      <c r="A268" s="23">
         <v>42094</v>
       </c>
       <c r="B268">
         <v>6.4260999999999804</v>
       </c>
-      <c r="C268" s="27">
+      <c r="C268" s="25">
         <f t="shared" si="7"/>
         <v>3.6390329230961971E-3</v>
       </c>
@@ -13692,13 +13709,13 @@
       </c>
     </row>
     <row r="269" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A269" s="25">
+      <c r="A269" s="23">
         <v>42124</v>
       </c>
       <c r="B269">
         <v>6.4806999999999801</v>
       </c>
-      <c r="C269" s="27">
+      <c r="C269" s="25">
         <f t="shared" si="7"/>
         <v>8.4965998039245871E-3</v>
       </c>
@@ -13708,13 +13725,13 @@
       </c>
     </row>
     <row r="270" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A270" s="25">
+      <c r="A270" s="23">
         <v>42153</v>
       </c>
       <c r="B270">
         <v>6.5354999999999803</v>
       </c>
-      <c r="C270" s="27">
+      <c r="C270" s="25">
         <f t="shared" si="7"/>
         <v>8.4558766799882612E-3</v>
       </c>
@@ -13724,13 +13741,13 @@
       </c>
     </row>
     <row r="271" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A271" s="25">
+      <c r="A271" s="23">
         <v>42185</v>
       </c>
       <c r="B271">
         <v>6.4546999999999803</v>
       </c>
-      <c r="C271" s="27">
+      <c r="C271" s="25">
         <f t="shared" ref="C271:C334" si="9">B271/B270-1</f>
         <v>-1.2363246882411527E-2</v>
       </c>
@@ -13740,13 +13757,13 @@
       </c>
     </row>
     <row r="272" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A272" s="25">
+      <c r="A272" s="23">
         <v>42216</v>
       </c>
       <c r="B272">
         <v>6.4663999999999797</v>
       </c>
-      <c r="C272" s="27">
+      <c r="C272" s="25">
         <f t="shared" si="9"/>
         <v>1.8126326552743155E-3</v>
       </c>
@@ -13756,13 +13773,13 @@
       </c>
     </row>
     <row r="273" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A273" s="25">
+      <c r="A273" s="23">
         <v>42247</v>
       </c>
       <c r="B273">
         <v>6.2846999999999804</v>
       </c>
-      <c r="C273" s="27">
+      <c r="C273" s="25">
         <f t="shared" si="9"/>
         <v>-2.8099096869974027E-2</v>
       </c>
@@ -13772,13 +13789,13 @@
       </c>
     </row>
     <row r="274" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A274" s="25">
+      <c r="A274" s="23">
         <v>42277</v>
       </c>
       <c r="B274">
         <v>6.0684999999999798</v>
       </c>
-      <c r="C274" s="27">
+      <c r="C274" s="25">
         <f t="shared" si="9"/>
         <v>-3.4401005616815694E-2</v>
       </c>
@@ -13788,13 +13805,13 @@
       </c>
     </row>
     <row r="275" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A275" s="25">
+      <c r="A275" s="23">
         <v>42307</v>
       </c>
       <c r="B275">
         <v>6.0770999999999802</v>
       </c>
-      <c r="C275" s="27">
+      <c r="C275" s="25">
         <f t="shared" si="9"/>
         <v>1.4171541567109536E-3</v>
       </c>
@@ -13804,13 +13821,13 @@
       </c>
     </row>
     <row r="276" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A276" s="25">
+      <c r="A276" s="23">
         <v>42338</v>
       </c>
       <c r="B276">
         <v>6.00589999999998</v>
       </c>
-      <c r="C276" s="27">
+      <c r="C276" s="25">
         <f t="shared" si="9"/>
         <v>-1.1716114594132132E-2</v>
       </c>
@@ -13820,13 +13837,13 @@
       </c>
     </row>
     <row r="277" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A277" s="25">
+      <c r="A277" s="23">
         <v>42369</v>
       </c>
       <c r="B277">
         <v>5.9279999999999804</v>
       </c>
-      <c r="C277" s="27">
+      <c r="C277" s="25">
         <f t="shared" si="9"/>
         <v>-1.2970578930718069E-2</v>
       </c>
@@ -13836,13 +13853,13 @@
       </c>
     </row>
     <row r="278" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A278" s="25">
+      <c r="A278" s="23">
         <v>42398</v>
       </c>
       <c r="B278">
         <v>5.7474999999999801</v>
       </c>
-      <c r="C278" s="27">
+      <c r="C278" s="25">
         <f t="shared" si="9"/>
         <v>-3.0448717948718063E-2</v>
       </c>
@@ -13852,13 +13869,13 @@
       </c>
     </row>
     <row r="279" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A279" s="25">
+      <c r="A279" s="23">
         <v>42429</v>
       </c>
       <c r="B279">
         <v>5.6432999999999804</v>
       </c>
-      <c r="C279" s="27">
+      <c r="C279" s="25">
         <f t="shared" si="9"/>
         <v>-1.8129621574597632E-2</v>
       </c>
@@ -13868,13 +13885,13 @@
       </c>
     </row>
     <row r="280" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A280" s="25">
+      <c r="A280" s="23">
         <v>42460</v>
       </c>
       <c r="B280">
         <v>5.6599999999999797</v>
       </c>
-      <c r="C280" s="27">
+      <c r="C280" s="25">
         <f t="shared" si="9"/>
         <v>2.9592614250526506E-3</v>
       </c>
@@ -13884,13 +13901,13 @@
       </c>
     </row>
     <row r="281" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A281" s="25">
+      <c r="A281" s="23">
         <v>42489</v>
       </c>
       <c r="B281">
         <v>5.7545999999999804</v>
       </c>
-      <c r="C281" s="27">
+      <c r="C281" s="25">
         <f t="shared" si="9"/>
         <v>1.6713780918728105E-2</v>
       </c>
@@ -13900,13 +13917,13 @@
       </c>
     </row>
     <row r="282" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A282" s="25">
+      <c r="A282" s="23">
         <v>42521</v>
       </c>
       <c r="B282">
         <v>5.8129999999999802</v>
       </c>
-      <c r="C282" s="27">
+      <c r="C282" s="25">
         <f t="shared" si="9"/>
         <v>1.0148403016717156E-2</v>
       </c>
@@ -13916,13 +13933,13 @@
       </c>
     </row>
     <row r="283" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A283" s="25">
+      <c r="A283" s="23">
         <v>42551</v>
       </c>
       <c r="B283">
         <v>5.7811999999999797</v>
       </c>
-      <c r="C283" s="27">
+      <c r="C283" s="25">
         <f t="shared" si="9"/>
         <v>-5.4704971615345821E-3</v>
       </c>
@@ -13932,13 +13949,13 @@
       </c>
     </row>
     <row r="284" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A284" s="25">
+      <c r="A284" s="23">
         <v>42580</v>
       </c>
       <c r="B284">
         <v>5.8692999999999804</v>
       </c>
-      <c r="C284" s="27">
+      <c r="C284" s="25">
         <f t="shared" si="9"/>
         <v>1.5239050716114422E-2</v>
       </c>
@@ -13948,13 +13965,13 @@
       </c>
     </row>
     <row r="285" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A285" s="25">
+      <c r="A285" s="23">
         <v>42613</v>
       </c>
       <c r="B285">
         <v>5.9472999999999798</v>
       </c>
-      <c r="C285" s="27">
+      <c r="C285" s="25">
         <f t="shared" si="9"/>
         <v>1.328948937692731E-2</v>
       </c>
@@ -13964,13 +13981,13 @@
       </c>
     </row>
     <row r="286" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A286" s="25">
+      <c r="A286" s="23">
         <v>42643</v>
       </c>
       <c r="B286">
         <v>5.9523999999999804</v>
       </c>
-      <c r="C286" s="27">
+      <c r="C286" s="25">
         <f t="shared" si="9"/>
         <v>8.575319893062705E-4</v>
       </c>
@@ -13980,13 +13997,13 @@
       </c>
     </row>
     <row r="287" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A287" s="25">
+      <c r="A287" s="23">
         <v>42674</v>
       </c>
       <c r="B287">
         <v>5.9474999999999802</v>
       </c>
-      <c r="C287" s="27">
+      <c r="C287" s="25">
         <f t="shared" si="9"/>
         <v>-8.2319736576841329E-4</v>
       </c>
@@ -13996,13 +14013,13 @@
       </c>
     </row>
     <row r="288" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A288" s="25">
+      <c r="A288" s="23">
         <v>42704</v>
       </c>
       <c r="B288">
         <v>6.0130999999999801</v>
       </c>
-      <c r="C288" s="27">
+      <c r="C288" s="25">
         <f t="shared" si="9"/>
         <v>1.1029844472467465E-2</v>
       </c>
@@ -14012,13 +14029,13 @@
       </c>
     </row>
     <row r="289" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A289" s="25">
+      <c r="A289" s="23">
         <v>42734</v>
       </c>
       <c r="B289">
         <v>6.0869999999999802</v>
       </c>
-      <c r="C289" s="27">
+      <c r="C289" s="25">
         <f t="shared" si="9"/>
         <v>1.2289833862733079E-2</v>
       </c>
@@ -14028,13 +14045,13 @@
       </c>
     </row>
     <row r="290" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A290" s="25">
+      <c r="A290" s="23">
         <v>42766</v>
       </c>
       <c r="B290">
         <v>6.1688999999999803</v>
       </c>
-      <c r="C290" s="27">
+      <c r="C290" s="25">
         <f t="shared" si="9"/>
         <v>1.3454903893543646E-2</v>
       </c>
@@ -14044,13 +14061,13 @@
       </c>
     </row>
     <row r="291" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A291" s="25">
+      <c r="A291" s="23">
         <v>42794</v>
       </c>
       <c r="B291">
         <v>6.2348999999999801</v>
       </c>
-      <c r="C291" s="27">
+      <c r="C291" s="25">
         <f t="shared" si="9"/>
         <v>1.0698827992024595E-2</v>
       </c>
@@ -14060,13 +14077,13 @@
       </c>
     </row>
     <row r="292" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A292" s="25">
+      <c r="A292" s="23">
         <v>42825</v>
       </c>
       <c r="B292">
         <v>6.2488999999999804</v>
       </c>
-      <c r="C292" s="27">
+      <c r="C292" s="25">
         <f t="shared" si="9"/>
         <v>2.2454249466712373E-3</v>
       </c>
@@ -14076,13 +14093,13 @@
       </c>
     </row>
     <row r="293" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A293" s="25">
+      <c r="A293" s="23">
         <v>42853</v>
       </c>
       <c r="B293">
         <v>6.2850999999999804</v>
       </c>
-      <c r="C293" s="27">
+      <c r="C293" s="25">
         <f t="shared" si="9"/>
         <v>5.7930195714446242E-3</v>
       </c>
@@ -14092,13 +14109,13 @@
       </c>
     </row>
     <row r="294" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A294" s="25">
+      <c r="A294" s="23">
         <v>42886</v>
       </c>
       <c r="B294">
         <v>6.3456999999999804</v>
       </c>
-      <c r="C294" s="27">
+      <c r="C294" s="25">
         <f t="shared" si="9"/>
         <v>9.6418513627467561E-3</v>
       </c>
@@ -14108,13 +14125,13 @@
       </c>
     </row>
     <row r="295" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A295" s="25">
+      <c r="A295" s="23">
         <v>42916</v>
       </c>
       <c r="B295">
         <v>6.3169999999999797</v>
       </c>
-      <c r="C295" s="27">
+      <c r="C295" s="25">
         <f t="shared" si="9"/>
         <v>-4.5227476874104555E-3</v>
       </c>
@@ -14124,13 +14141,13 @@
       </c>
     </row>
     <row r="296" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A296" s="25">
+      <c r="A296" s="23">
         <v>42947</v>
       </c>
       <c r="B296">
         <v>6.39539999999998</v>
       </c>
-      <c r="C296" s="27">
+      <c r="C296" s="25">
         <f t="shared" si="9"/>
         <v>1.2410954567041443E-2</v>
       </c>
@@ -14140,13 +14157,13 @@
       </c>
     </row>
     <row r="297" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A297" s="25">
+      <c r="A297" s="23">
         <v>42978</v>
       </c>
       <c r="B297">
         <v>6.3501999999999796</v>
       </c>
-      <c r="C297" s="27">
+      <c r="C297" s="25">
         <f t="shared" si="9"/>
         <v>-7.0675798229978826E-3</v>
       </c>
@@ -14156,13 +14173,13 @@
       </c>
     </row>
     <row r="298" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A298" s="25">
+      <c r="A298" s="23">
         <v>43007</v>
       </c>
       <c r="B298">
         <v>6.3744999999999798</v>
       </c>
-      <c r="C298" s="27">
+      <c r="C298" s="25">
         <f t="shared" si="9"/>
         <v>3.8266511290983019E-3</v>
       </c>
@@ -14172,13 +14189,13 @@
       </c>
     </row>
     <row r="299" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A299" s="25">
+      <c r="A299" s="23">
         <v>43039</v>
       </c>
       <c r="B299">
         <v>6.38969999999998</v>
       </c>
-      <c r="C299" s="27">
+      <c r="C299" s="25">
         <f t="shared" si="9"/>
         <v>2.3845007451566147E-3</v>
       </c>
@@ -14188,13 +14205,13 @@
       </c>
     </row>
     <row r="300" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A300" s="25">
+      <c r="A300" s="23">
         <v>43069</v>
       </c>
       <c r="B300">
         <v>6.3723999999999803</v>
       </c>
-      <c r="C300" s="27">
+      <c r="C300" s="25">
         <f t="shared" si="9"/>
         <v>-2.7074823544140925E-3</v>
       </c>
@@ -14204,13 +14221,13 @@
       </c>
     </row>
     <row r="301" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A301" s="25">
+      <c r="A301" s="23">
         <v>43098</v>
       </c>
       <c r="B301">
         <v>6.4706999999999804</v>
       </c>
-      <c r="C301" s="27">
+      <c r="C301" s="25">
         <f t="shared" si="9"/>
         <v>1.5425899190258052E-2</v>
       </c>
@@ -14220,13 +14237,13 @@
       </c>
     </row>
     <row r="302" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A302" s="25">
+      <c r="A302" s="23">
         <v>43131</v>
       </c>
       <c r="B302">
         <v>6.5746999999999796</v>
       </c>
-      <c r="C302" s="27">
+      <c r="C302" s="25">
         <f t="shared" si="9"/>
         <v>1.6072449657687615E-2</v>
       </c>
@@ -14236,13 +14253,13 @@
       </c>
     </row>
     <row r="303" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A303" s="25">
+      <c r="A303" s="23">
         <v>43159</v>
       </c>
       <c r="B303">
         <v>6.4887999999999799</v>
       </c>
-      <c r="C303" s="27">
+      <c r="C303" s="25">
         <f t="shared" si="9"/>
         <v>-1.3065234915661583E-2</v>
       </c>
@@ -14252,13 +14269,13 @@
       </c>
     </row>
     <row r="304" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A304" s="25">
+      <c r="A304" s="23">
         <v>43189</v>
       </c>
       <c r="B304">
         <v>6.4545999999999797</v>
       </c>
-      <c r="C304" s="27">
+      <c r="C304" s="25">
         <f t="shared" si="9"/>
         <v>-5.2706201454815194E-3</v>
       </c>
@@ -14268,13 +14285,13 @@
       </c>
     </row>
     <row r="305" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A305" s="25">
+      <c r="A305" s="23">
         <v>43220</v>
       </c>
       <c r="B305">
         <v>6.4800999999999798</v>
       </c>
-      <c r="C305" s="27">
+      <c r="C305" s="25">
         <f t="shared" si="9"/>
         <v>3.9506708394014822E-3</v>
       </c>
@@ -14284,13 +14301,13 @@
       </c>
     </row>
     <row r="306" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A306" s="25">
+      <c r="A306" s="23">
         <v>43251</v>
       </c>
       <c r="B306">
         <v>6.51389999999998</v>
       </c>
-      <c r="C306" s="27">
+      <c r="C306" s="25">
         <f t="shared" si="9"/>
         <v>5.2159688893691492E-3</v>
       </c>
@@ -14300,13 +14317,13 @@
       </c>
     </row>
     <row r="307" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A307" s="25">
+      <c r="A307" s="23">
         <v>43280</v>
       </c>
       <c r="B307">
         <v>6.5560999999999803</v>
       </c>
-      <c r="C307" s="27">
+      <c r="C307" s="25">
         <f t="shared" si="9"/>
         <v>6.4784537680959708E-3</v>
       </c>
@@ -14316,13 +14333,13 @@
       </c>
     </row>
     <row r="308" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A308" s="25">
+      <c r="A308" s="23">
         <v>43312</v>
       </c>
       <c r="B308">
         <v>6.5968999999999802</v>
       </c>
-      <c r="C308" s="27">
+      <c r="C308" s="25">
         <f t="shared" si="9"/>
         <v>6.2232119705312172E-3</v>
       </c>
@@ -14332,13 +14349,13 @@
       </c>
     </row>
     <row r="309" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A309" s="25">
+      <c r="A309" s="23">
         <v>43343</v>
       </c>
       <c r="B309">
         <v>6.6080999999999799</v>
       </c>
-      <c r="C309" s="27">
+      <c r="C309" s="25">
         <f t="shared" si="9"/>
         <v>1.6977671330473676E-3</v>
       </c>
@@ -14348,13 +14365,13 @@
       </c>
     </row>
     <row r="310" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A310" s="25">
+      <c r="A310" s="23">
         <v>43371</v>
       </c>
       <c r="B310">
         <v>6.6235999999999802</v>
       </c>
-      <c r="C310" s="27">
+      <c r="C310" s="25">
         <f t="shared" si="9"/>
         <v>2.3456061500279901E-3</v>
       </c>
@@ -14364,13 +14381,13 @@
       </c>
     </row>
     <row r="311" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A311" s="25">
+      <c r="A311" s="23">
         <v>43404</v>
       </c>
       <c r="B311">
         <v>6.44339999999998</v>
       </c>
-      <c r="C311" s="27">
+      <c r="C311" s="25">
         <f t="shared" si="9"/>
         <v>-2.7205749139440849E-2</v>
       </c>
@@ -14380,13 +14397,13 @@
       </c>
     </row>
     <row r="312" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A312" s="25">
+      <c r="A312" s="23">
         <v>43434</v>
       </c>
       <c r="B312">
         <v>6.41709999999998</v>
       </c>
-      <c r="C312" s="27">
+      <c r="C312" s="25">
         <f t="shared" si="9"/>
         <v>-4.0816959990067625E-3</v>
       </c>
@@ -14396,13 +14413,13 @@
       </c>
     </row>
     <row r="313" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A313" s="25">
+      <c r="A313" s="23">
         <v>43465</v>
       </c>
       <c r="B313">
         <v>6.2153999999999803</v>
       </c>
-      <c r="C313" s="27">
+      <c r="C313" s="25">
         <f t="shared" si="9"/>
         <v>-3.143164357731687E-2</v>
       </c>
@@ -14412,13 +14429,13 @@
       </c>
     </row>
     <row r="314" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A314" s="25">
+      <c r="A314" s="23">
         <v>43496</v>
       </c>
       <c r="B314">
         <v>6.3720999999999801</v>
       </c>
-      <c r="C314" s="27">
+      <c r="C314" s="25">
         <f t="shared" si="9"/>
         <v>2.5211571258487053E-2</v>
       </c>
@@ -14428,13 +14445,13 @@
       </c>
     </row>
     <row r="315" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A315" s="25">
+      <c r="A315" s="23">
         <v>43524</v>
       </c>
       <c r="B315">
         <v>6.4750999999999799</v>
       </c>
-      <c r="C315" s="27">
+      <c r="C315" s="25">
         <f t="shared" si="9"/>
         <v>1.6164215878595733E-2</v>
       </c>
@@ -14444,13 +14461,13 @@
       </c>
     </row>
     <row r="316" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A316" s="25">
+      <c r="A316" s="23">
         <v>43553</v>
       </c>
       <c r="B316">
         <v>6.5234999999999799</v>
       </c>
-      <c r="C316" s="27">
+      <c r="C316" s="25">
         <f t="shared" si="9"/>
         <v>7.4747880341616835E-3</v>
       </c>
@@ -14460,13 +14477,13 @@
       </c>
     </row>
     <row r="317" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A317" s="25">
+      <c r="A317" s="23">
         <v>43585</v>
       </c>
       <c r="B317">
         <v>6.6464999999999801</v>
       </c>
-      <c r="C317" s="27">
+      <c r="C317" s="25">
         <f t="shared" si="9"/>
         <v>1.8854909174522927E-2</v>
       </c>
@@ -14476,13 +14493,13 @@
       </c>
     </row>
     <row r="318" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A318" s="25">
+      <c r="A318" s="23">
         <v>43616</v>
       </c>
       <c r="B318">
         <v>6.5719999999999796</v>
       </c>
-      <c r="C318" s="27">
+      <c r="C318" s="25">
         <f t="shared" si="9"/>
         <v>-1.1208906943504182E-2</v>
       </c>
@@ -14492,13 +14509,13 @@
       </c>
     </row>
     <row r="319" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A319" s="25">
+      <c r="A319" s="23">
         <v>43644</v>
       </c>
       <c r="B319">
         <v>6.6785999999999799</v>
       </c>
-      <c r="C319" s="27">
+      <c r="C319" s="25">
         <f t="shared" si="9"/>
         <v>1.622032866707257E-2</v>
       </c>
@@ -14508,13 +14525,13 @@
       </c>
     </row>
     <row r="320" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A320" s="25">
+      <c r="A320" s="23">
         <v>43677</v>
       </c>
       <c r="B320">
         <v>6.6653999999999796</v>
       </c>
-      <c r="C320" s="27">
+      <c r="C320" s="25">
         <f t="shared" si="9"/>
         <v>-1.9764621327823528E-3</v>
       </c>
@@ -14524,13 +14541,13 @@
       </c>
     </row>
     <row r="321" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A321" s="25">
+      <c r="A321" s="23">
         <v>43707</v>
       </c>
       <c r="B321">
         <v>6.5826999999999796</v>
       </c>
-      <c r="C321" s="27">
+      <c r="C321" s="25">
         <f t="shared" si="9"/>
         <v>-1.2407357397905661E-2</v>
       </c>
@@ -14540,13 +14557,13 @@
       </c>
     </row>
     <row r="322" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A322" s="25">
+      <c r="A322" s="23">
         <v>43738</v>
       </c>
       <c r="B322">
         <v>6.5793999999999802</v>
       </c>
-      <c r="C322" s="27">
+      <c r="C322" s="25">
         <f t="shared" si="9"/>
         <v>-5.013140504654956E-4</v>
       </c>
@@ -14556,13 +14573,13 @@
       </c>
     </row>
     <row r="323" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A323" s="25">
+      <c r="A323" s="23">
         <v>43769</v>
       </c>
       <c r="B323">
         <v>6.5675999999999801</v>
       </c>
-      <c r="C323" s="27">
+      <c r="C323" s="25">
         <f t="shared" si="9"/>
         <v>-1.7934766088093523E-3</v>
       </c>
@@ -14572,13 +14589,13 @@
       </c>
     </row>
     <row r="324" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A324" s="25">
+      <c r="A324" s="23">
         <v>43798</v>
       </c>
       <c r="B324">
         <v>6.6064999999999801</v>
       </c>
-      <c r="C324" s="27">
+      <c r="C324" s="25">
         <f t="shared" si="9"/>
         <v>5.9230160180279157E-3</v>
       </c>
@@ -14588,13 +14605,13 @@
       </c>
     </row>
     <row r="325" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A325" s="25">
+      <c r="A325" s="23">
         <v>43830</v>
       </c>
       <c r="B325">
         <v>6.7259999999999804</v>
       </c>
-      <c r="C325" s="27">
+      <c r="C325" s="25">
         <f t="shared" si="9"/>
         <v>1.808824642397644E-2</v>
       </c>
@@ -14604,13 +14621,13 @@
       </c>
     </row>
     <row r="326" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A326" s="25">
+      <c r="A326" s="23">
         <v>43861</v>
       </c>
       <c r="B326">
         <v>6.7326999999999799</v>
       </c>
-      <c r="C326" s="27">
+      <c r="C326" s="25">
         <f t="shared" si="9"/>
         <v>9.9613440380608154E-4</v>
       </c>
@@ -14620,13 +14637,13 @@
       </c>
     </row>
     <row r="327" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A327" s="25">
+      <c r="A327" s="23">
         <v>43889</v>
       </c>
       <c r="B327">
         <v>6.5411999999999804</v>
       </c>
-      <c r="C327" s="27">
+      <c r="C327" s="25">
         <f t="shared" si="9"/>
         <v>-2.8443269416430272E-2</v>
       </c>
@@ -14636,13 +14653,13 @@
       </c>
     </row>
     <row r="328" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A328" s="25">
+      <c r="A328" s="23">
         <v>43921</v>
       </c>
       <c r="B328">
         <v>5.6602999999999799</v>
       </c>
-      <c r="C328" s="27">
+      <c r="C328" s="25">
         <f t="shared" si="9"/>
         <v>-0.13466947960618891</v>
       </c>
@@ -14652,13 +14669,13 @@
       </c>
     </row>
     <row r="329" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A329" s="25">
+      <c r="A329" s="23">
         <v>43951</v>
       </c>
       <c r="B329">
         <v>5.9059999999999802</v>
       </c>
-      <c r="C329" s="27">
+      <c r="C329" s="25">
         <f t="shared" si="9"/>
         <v>4.3407593237107855E-2</v>
       </c>
@@ -14668,13 +14685,13 @@
       </c>
     </row>
     <row r="330" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A330" s="25">
+      <c r="A330" s="23">
         <v>43980</v>
       </c>
       <c r="B330">
         <v>6.0743999999999803</v>
       </c>
-      <c r="C330" s="27">
+      <c r="C330" s="25">
         <f t="shared" si="9"/>
         <v>2.8513376227565335E-2</v>
       </c>
@@ -14684,13 +14701,13 @@
       </c>
     </row>
     <row r="331" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A331" s="25">
+      <c r="A331" s="23">
         <v>44012</v>
       </c>
       <c r="B331">
         <v>6.2168999999999803</v>
       </c>
-      <c r="C331" s="27">
+      <c r="C331" s="25">
         <f t="shared" si="9"/>
         <v>2.3459107072303587E-2</v>
       </c>
@@ -14700,13 +14717,13 @@
       </c>
     </row>
     <row r="332" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A332" s="25">
+      <c r="A332" s="23">
         <v>44043</v>
       </c>
       <c r="B332">
         <v>6.3249999999999797</v>
       </c>
-      <c r="C332" s="27">
+      <c r="C332" s="25">
         <f t="shared" si="9"/>
         <v>1.7388087310395761E-2</v>
       </c>
@@ -14716,13 +14733,13 @@
       </c>
     </row>
     <row r="333" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A333" s="25">
+      <c r="A333" s="23">
         <v>44074</v>
       </c>
       <c r="B333">
         <v>6.5278999999999803</v>
       </c>
-      <c r="C333" s="27">
+      <c r="C333" s="25">
         <f t="shared" si="9"/>
         <v>3.2079051383399504E-2</v>
       </c>
@@ -14732,13 +14749,13 @@
       </c>
     </row>
     <row r="334" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A334" s="25">
+      <c r="A334" s="23">
         <v>44104</v>
       </c>
       <c r="B334">
         <v>6.5150999999999799</v>
       </c>
-      <c r="C334" s="27">
+      <c r="C334" s="25">
         <f t="shared" si="9"/>
         <v>-1.9608143507100495E-3</v>
       </c>
@@ -14748,13 +14765,13 @@
       </c>
     </row>
     <row r="335" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A335" s="25">
+      <c r="A335" s="23">
         <v>44134</v>
       </c>
       <c r="B335">
         <v>6.49449999999998</v>
       </c>
-      <c r="C335" s="27">
+      <c r="C335" s="25">
         <f t="shared" ref="C335:C389" si="11">B335/B334-1</f>
         <v>-3.1618854660711015E-3</v>
       </c>
@@ -14764,13 +14781,13 @@
       </c>
     </row>
     <row r="336" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A336" s="25">
+      <c r="A336" s="23">
         <v>44165</v>
       </c>
       <c r="B336">
         <v>6.9328999999999796</v>
       </c>
-      <c r="C336" s="27">
+      <c r="C336" s="25">
         <f t="shared" si="11"/>
         <v>6.7503271999384218E-2</v>
       </c>
@@ -14780,13 +14797,13 @@
       </c>
     </row>
     <row r="337" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A337" s="25">
+      <c r="A337" s="23">
         <v>44196</v>
       </c>
       <c r="B337">
         <v>7.1934999999999798</v>
       </c>
-      <c r="C337" s="27">
+      <c r="C337" s="25">
         <f t="shared" si="11"/>
         <v>3.7588887767024071E-2</v>
       </c>
@@ -14796,13 +14813,13 @@
       </c>
     </row>
     <row r="338" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A338" s="25">
+      <c r="A338" s="23">
         <v>44225</v>
       </c>
       <c r="B338">
         <v>7.2941999999999796</v>
       </c>
-      <c r="C338" s="27">
+      <c r="C338" s="25">
         <f t="shared" si="11"/>
         <v>1.3998748870508004E-2</v>
       </c>
@@ -14812,13 +14829,13 @@
       </c>
     </row>
     <row r="339" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A339" s="25">
+      <c r="A339" s="23">
         <v>44253</v>
       </c>
       <c r="B339">
         <v>7.5237999999999703</v>
       </c>
-      <c r="C339" s="27">
+      <c r="C339" s="25">
         <f t="shared" si="11"/>
         <v>3.147706396863148E-2</v>
       </c>
@@ -14828,13 +14845,13 @@
       </c>
     </row>
     <row r="340" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A340" s="25">
+      <c r="A340" s="23">
         <v>44286</v>
       </c>
       <c r="B340">
         <v>7.6472999999999702</v>
       </c>
-      <c r="C340" s="27">
+      <c r="C340" s="25">
         <f t="shared" si="11"/>
         <v>1.6414577739971792E-2</v>
       </c>
@@ -14844,13 +14861,13 @@
       </c>
     </row>
     <row r="341" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A341" s="25">
+      <c r="A341" s="23">
         <v>44316</v>
       </c>
       <c r="B341">
         <v>7.7937999999999699</v>
       </c>
-      <c r="C341" s="27">
+      <c r="C341" s="25">
         <f t="shared" si="11"/>
         <v>1.9157088122605304E-2</v>
       </c>
@@ -14860,13 +14877,13 @@
       </c>
     </row>
     <row r="342" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A342" s="25">
+      <c r="A342" s="23">
         <v>44347</v>
       </c>
       <c r="B342">
         <v>7.8792999999999704</v>
       </c>
-      <c r="C342" s="27">
+      <c r="C342" s="25">
         <f t="shared" si="11"/>
         <v>1.0970258410531564E-2</v>
       </c>
@@ -14876,13 +14893,13 @@
       </c>
     </row>
     <row r="343" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A343" s="25">
+      <c r="A343" s="23">
         <v>44377</v>
       </c>
       <c r="B343">
         <v>7.9239999999999702</v>
       </c>
-      <c r="C343" s="27">
+      <c r="C343" s="25">
         <f t="shared" si="11"/>
         <v>5.6730927874304449E-3</v>
       </c>
@@ -14892,13 +14909,13 @@
       </c>
     </row>
     <row r="344" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A344" s="25">
+      <c r="A344" s="23">
         <v>44407</v>
       </c>
       <c r="B344">
         <v>7.8821999999999699</v>
       </c>
-      <c r="C344" s="27">
+      <c r="C344" s="25">
         <f t="shared" si="11"/>
         <v>-5.2751135790005677E-3</v>
       </c>
@@ -14908,13 +14925,13 @@
       </c>
     </row>
     <row r="345" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A345" s="25">
+      <c r="A345" s="23">
         <v>44439</v>
       </c>
       <c r="B345">
         <v>8.0666999999999707</v>
       </c>
-      <c r="C345" s="27">
+      <c r="C345" s="25">
         <f t="shared" si="11"/>
         <v>2.3407170586892123E-2</v>
       </c>
@@ -14924,13 +14941,13 @@
       </c>
     </row>
     <row r="346" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A346" s="25">
+      <c r="A346" s="23">
         <v>44469</v>
       </c>
       <c r="B346">
         <v>8.1159999999999695</v>
       </c>
-      <c r="C346" s="27">
+      <c r="C346" s="25">
         <f t="shared" si="11"/>
         <v>6.1115449936155475E-3</v>
       </c>
@@ -14940,13 +14957,13 @@
       </c>
     </row>
     <row r="347" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A347" s="25">
+      <c r="A347" s="23">
         <v>44498</v>
       </c>
       <c r="B347">
         <v>8.2536999999999701</v>
       </c>
-      <c r="C347" s="27">
+      <c r="C347" s="25">
         <f t="shared" si="11"/>
         <v>1.6966485953672006E-2</v>
       </c>
@@ -14956,13 +14973,13 @@
       </c>
     </row>
     <row r="348" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A348" s="25">
+      <c r="A348" s="23">
         <v>44530</v>
       </c>
       <c r="B348">
         <v>8.1017999999999706</v>
       </c>
-      <c r="C348" s="27">
+      <c r="C348" s="25">
         <f t="shared" si="11"/>
         <v>-1.840386735645827E-2</v>
       </c>
@@ -14972,13 +14989,13 @@
       </c>
     </row>
     <row r="349" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A349" s="25">
+      <c r="A349" s="23">
         <v>44561</v>
       </c>
       <c r="B349">
         <v>8.1230999999999707</v>
       </c>
-      <c r="C349" s="27">
+      <c r="C349" s="25">
         <f t="shared" si="11"/>
         <v>2.6290453973192296E-3</v>
       </c>
@@ -14988,13 +15005,13 @@
       </c>
     </row>
     <row r="350" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A350" s="25">
+      <c r="A350" s="23">
         <v>44592</v>
       </c>
       <c r="B350">
         <v>7.9577999999999696</v>
       </c>
-      <c r="C350" s="27">
+      <c r="C350" s="25">
         <f t="shared" si="11"/>
         <v>-2.0349374007460397E-2</v>
       </c>
@@ -15004,13 +15021,13 @@
       </c>
     </row>
     <row r="351" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A351" s="25">
+      <c r="A351" s="23">
         <v>44620</v>
       </c>
       <c r="B351">
         <v>7.9240999999999699</v>
       </c>
-      <c r="C351" s="27">
+      <c r="C351" s="25">
         <f t="shared" si="11"/>
         <v>-4.2348387745356764E-3</v>
       </c>
@@ -15020,13 +15037,13 @@
       </c>
     </row>
     <row r="352" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A352" s="25">
+      <c r="A352" s="23">
         <v>44651</v>
       </c>
       <c r="B352">
         <v>7.9441999999999702</v>
       </c>
-      <c r="C352" s="27">
+      <c r="C352" s="25">
         <f t="shared" si="11"/>
         <v>2.5365656667635239E-3</v>
       </c>
@@ -15036,13 +15053,13 @@
       </c>
     </row>
     <row r="353" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A353" s="25">
+      <c r="A353" s="23">
         <v>44680</v>
       </c>
       <c r="B353">
         <v>7.8804999999999703</v>
       </c>
-      <c r="C353" s="27">
+      <c r="C353" s="25">
         <f t="shared" si="11"/>
         <v>-8.0184285390599852E-3</v>
       </c>
@@ -15052,13 +15069,13 @@
       </c>
     </row>
     <row r="354" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A354" s="25">
+      <c r="A354" s="23">
         <v>44712</v>
       </c>
       <c r="B354">
         <v>7.7774999999999697</v>
       </c>
-      <c r="C354" s="27">
+      <c r="C354" s="25">
         <f t="shared" si="11"/>
         <v>-1.3070236660110535E-2</v>
       </c>
@@ -15068,13 +15085,13 @@
       </c>
     </row>
     <row r="355" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A355" s="25">
+      <c r="A355" s="23">
         <v>44742</v>
       </c>
       <c r="B355">
         <v>7.4986999999999702</v>
       </c>
-      <c r="C355" s="27">
+      <c r="C355" s="25">
         <f t="shared" si="11"/>
         <v>-3.5846994535519205E-2</v>
       </c>
@@ -15084,13 +15101,13 @@
       </c>
     </row>
     <row r="356" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A356" s="25">
+      <c r="A356" s="23">
         <v>44771</v>
       </c>
       <c r="B356">
         <v>7.5798999999999799</v>
       </c>
-      <c r="C356" s="27">
+      <c r="C356" s="25">
         <f t="shared" si="11"/>
         <v>1.0828543614227915E-2</v>
       </c>
@@ -15100,13 +15117,13 @@
       </c>
     </row>
     <row r="357" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A357" s="25">
+      <c r="A357" s="23">
         <v>44804</v>
       </c>
       <c r="B357">
         <v>7.6336999999999797</v>
       </c>
-      <c r="C357" s="27">
+      <c r="C357" s="25">
         <f t="shared" si="11"/>
         <v>7.0977189672687402E-3</v>
       </c>
@@ -15116,13 +15133,13 @@
       </c>
     </row>
     <row r="358" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A358" s="25">
+      <c r="A358" s="23">
         <v>44834</v>
       </c>
       <c r="B358">
         <v>7.4421999999999802</v>
       </c>
-      <c r="C358" s="27">
+      <c r="C358" s="25">
         <f t="shared" si="11"/>
         <v>-2.5086131233870823E-2</v>
       </c>
@@ -15132,13 +15149,13 @@
       </c>
     </row>
     <row r="359" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A359" s="25">
+      <c r="A359" s="23">
         <v>44865</v>
       </c>
       <c r="B359">
         <v>7.50629999999998</v>
       </c>
-      <c r="C359" s="27">
+      <c r="C359" s="25">
         <f t="shared" si="11"/>
         <v>8.61304452984335E-3</v>
       </c>
@@ -15148,13 +15165,13 @@
       </c>
     </row>
     <row r="360" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A360" s="25">
+      <c r="A360" s="23">
         <v>44895</v>
       </c>
       <c r="B360">
         <v>7.5759999999999801</v>
       </c>
-      <c r="C360" s="27">
+      <c r="C360" s="25">
         <f t="shared" si="11"/>
         <v>9.2855334852057769E-3</v>
       </c>
@@ -15164,13 +15181,13 @@
       </c>
     </row>
     <row r="361" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A361" s="25">
+      <c r="A361" s="23">
         <v>44925</v>
       </c>
       <c r="B361">
         <v>7.57109999999998</v>
       </c>
-      <c r="C361" s="27">
+      <c r="C361" s="25">
         <f t="shared" si="11"/>
         <v>-6.4677930306233922E-4</v>
       </c>
@@ -15180,13 +15197,13 @@
       </c>
     </row>
     <row r="362" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A362" s="25">
+      <c r="A362" s="23">
         <v>44957</v>
       </c>
       <c r="B362">
         <v>7.7373999999999699</v>
       </c>
-      <c r="C362" s="27">
+      <c r="C362" s="25">
         <f t="shared" si="11"/>
         <v>2.1965104146027592E-2</v>
       </c>
@@ -15196,13 +15213,13 @@
       </c>
     </row>
     <row r="363" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A363" s="25">
+      <c r="A363" s="23">
         <v>44985</v>
       </c>
       <c r="B363">
         <v>7.7096999999999696</v>
       </c>
-      <c r="C363" s="27">
+      <c r="C363" s="25">
         <f t="shared" si="11"/>
         <v>-3.5800139581771973E-3</v>
       </c>
@@ -15212,13 +15229,13 @@
       </c>
     </row>
     <row r="364" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A364" s="25">
+      <c r="A364" s="23">
         <v>45016</v>
       </c>
       <c r="B364">
         <v>7.6701999999999702</v>
       </c>
-      <c r="C364" s="27">
+      <c r="C364" s="25">
         <f t="shared" si="11"/>
         <v>-5.1234159565222148E-3</v>
       </c>
@@ -15228,13 +15245,13 @@
       </c>
     </row>
     <row r="365" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A365" s="25">
+      <c r="A365" s="23">
         <v>45044</v>
       </c>
       <c r="B365">
         <v>7.7226999999999704</v>
       </c>
-      <c r="C365" s="27">
+      <c r="C365" s="25">
         <f t="shared" si="11"/>
         <v>6.844671586138551E-3</v>
       </c>
@@ -15244,13 +15261,13 @@
       </c>
     </row>
     <row r="366" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A366" s="25">
+      <c r="A366" s="23">
         <v>45077</v>
       </c>
       <c r="B366">
         <v>7.7276999999999703</v>
       </c>
-      <c r="C366" s="27">
+      <c r="C366" s="25">
         <f t="shared" si="11"/>
         <v>6.4744195682853167E-4</v>
       </c>
@@ -15260,13 +15277,13 @@
       </c>
     </row>
     <row r="367" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A367" s="25">
+      <c r="A367" s="23">
         <v>45107</v>
       </c>
       <c r="B367">
         <v>7.8890999999999698</v>
       </c>
-      <c r="C367" s="27">
+      <c r="C367" s="25">
         <f t="shared" si="11"/>
         <v>2.0885903955898844E-2</v>
       </c>
@@ -15276,13 +15293,13 @@
       </c>
     </row>
     <row r="368" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A368" s="25">
+      <c r="A368" s="23">
         <v>45138</v>
       </c>
       <c r="B368">
         <v>7.9908999999999697</v>
       </c>
-      <c r="C368" s="27">
+      <c r="C368" s="25">
         <f t="shared" si="11"/>
         <v>1.2903880037013149E-2</v>
       </c>
@@ -15292,13 +15309,13 @@
       </c>
     </row>
     <row r="369" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A369" s="25">
+      <c r="A369" s="23">
         <v>45169</v>
       </c>
       <c r="B369">
         <v>7.9965999999999697</v>
       </c>
-      <c r="C369" s="27">
+      <c r="C369" s="25">
         <f t="shared" si="11"/>
         <v>7.1331139170816016E-4</v>
       </c>
@@ -15308,13 +15325,13 @@
       </c>
     </row>
     <row r="370" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A370" s="25">
+      <c r="A370" s="23">
         <v>45198</v>
       </c>
       <c r="B370">
         <v>8.0043999999999702</v>
       </c>
-      <c r="C370" s="27">
+      <c r="C370" s="25">
         <f t="shared" si="11"/>
         <v>9.7541455118421716E-4</v>
       </c>
@@ -15324,13 +15341,13 @@
       </c>
     </row>
     <row r="371" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A371" s="25">
+      <c r="A371" s="23">
         <v>45230</v>
       </c>
       <c r="B371">
         <v>7.88369999999997</v>
       </c>
-      <c r="C371" s="27">
+      <c r="C371" s="25">
         <f t="shared" si="11"/>
         <v>-1.5079206436459991E-2</v>
       </c>
@@ -15340,13 +15357,13 @@
       </c>
     </row>
     <row r="372" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A372" s="25">
+      <c r="A372" s="23">
         <v>45260</v>
       </c>
       <c r="B372">
         <v>8.0708999999999698</v>
       </c>
-      <c r="C372" s="27">
+      <c r="C372" s="25">
         <f t="shared" si="11"/>
         <v>2.3745195783705597E-2</v>
       </c>
@@ -15356,13 +15373,13 @@
       </c>
     </row>
     <row r="373" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A373" s="25">
+      <c r="A373" s="23">
         <v>45289</v>
       </c>
       <c r="B373">
         <v>8.2749999999999702</v>
       </c>
-      <c r="C373" s="27">
+      <c r="C373" s="25">
         <f t="shared" si="11"/>
         <v>2.5288381717032848E-2</v>
       </c>
@@ -15372,13 +15389,13 @@
       </c>
     </row>
     <row r="374" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A374" s="25">
+      <c r="A374" s="23">
         <v>45322</v>
       </c>
       <c r="B374">
         <v>8.3135999999999708</v>
       </c>
-      <c r="C374" s="27">
+      <c r="C374" s="25">
         <f t="shared" si="11"/>
         <v>4.6646525679758799E-3</v>
       </c>
@@ -15388,13 +15405,13 @@
       </c>
     </row>
     <row r="375" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A375" s="25">
+      <c r="A375" s="23">
         <v>45351</v>
       </c>
       <c r="B375">
         <v>8.4807999999999701</v>
       </c>
-      <c r="C375" s="27">
+      <c r="C375" s="25">
         <f t="shared" si="11"/>
         <v>2.0111624326405009E-2</v>
       </c>
@@ -15404,13 +15421,13 @@
       </c>
     </row>
     <row r="376" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A376" s="25">
+      <c r="A376" s="23">
         <v>45380</v>
       </c>
       <c r="B376">
         <v>8.6220999999999695</v>
       </c>
-      <c r="C376" s="27">
+      <c r="C376" s="25">
         <f t="shared" si="11"/>
         <v>1.6661164041128274E-2</v>
       </c>
@@ -15420,13 +15437,13 @@
       </c>
     </row>
     <row r="377" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A377" s="25">
+      <c r="A377" s="23">
         <v>45412</v>
       </c>
       <c r="B377">
         <v>8.5712999999999706</v>
       </c>
-      <c r="C377" s="27">
+      <c r="C377" s="25">
         <f t="shared" si="11"/>
         <v>-5.891836095614611E-3</v>
       </c>
@@ -15436,13 +15453,13 @@
       </c>
     </row>
     <row r="378" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A378" s="25">
+      <c r="A378" s="23">
         <v>45443</v>
       </c>
       <c r="B378">
         <v>8.7103999999999697</v>
       </c>
-      <c r="C378" s="27">
+      <c r="C378" s="25">
         <f t="shared" si="11"/>
         <v>1.6228576761984748E-2</v>
       </c>
@@ -15452,13 +15469,13 @@
       </c>
     </row>
     <row r="379" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A379" s="25">
+      <c r="A379" s="23">
         <v>45471</v>
       </c>
       <c r="B379">
         <v>8.7555999999999692</v>
       </c>
-      <c r="C379" s="27">
+      <c r="C379" s="25">
         <f t="shared" si="11"/>
         <v>5.1891991182952957E-3</v>
       </c>
@@ -15468,13 +15485,13 @@
       </c>
     </row>
     <row r="380" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A380" s="25">
+      <c r="A380" s="23">
         <v>45504</v>
       </c>
       <c r="B380">
         <v>8.8458999999999701</v>
       </c>
-      <c r="C380" s="27">
+      <c r="C380" s="25">
         <f t="shared" si="11"/>
         <v>1.0313399424368486E-2</v>
       </c>
@@ -15484,13 +15501,13 @@
       </c>
     </row>
     <row r="381" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A381" s="25">
+      <c r="A381" s="23">
         <v>45534</v>
       </c>
       <c r="B381">
         <v>8.93209999999997</v>
       </c>
-      <c r="C381" s="27">
+      <c r="C381" s="25">
         <f t="shared" si="11"/>
         <v>9.7446274545269773E-3</v>
       </c>
@@ -15500,13 +15517,13 @@
       </c>
     </row>
     <row r="382" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A382" s="25">
+      <c r="A382" s="23">
         <v>45565</v>
       </c>
       <c r="B382">
         <v>9.07839999999997</v>
       </c>
-      <c r="C382" s="27">
+      <c r="C382" s="25">
         <f t="shared" si="11"/>
         <v>1.6379126969021884E-2</v>
       </c>
@@ -15516,13 +15533,13 @@
       </c>
     </row>
     <row r="383" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A383" s="25">
+      <c r="A383" s="23">
         <v>45596</v>
       </c>
       <c r="B383">
         <v>9.1453999999999702</v>
       </c>
-      <c r="C383" s="27">
+      <c r="C383" s="25">
         <f t="shared" si="11"/>
         <v>7.3801550934085025E-3</v>
       </c>
@@ -15532,13 +15549,13 @@
       </c>
     </row>
     <row r="384" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A384" s="25">
+      <c r="A384" s="23">
         <v>45625</v>
       </c>
       <c r="B384">
         <v>9.35509999999997</v>
       </c>
-      <c r="C384" s="27">
+      <c r="C384" s="25">
         <f t="shared" si="11"/>
         <v>2.2929560216064848E-2</v>
       </c>
@@ -15548,13 +15565,13 @@
       </c>
     </row>
     <row r="385" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A385" s="25">
+      <c r="A385" s="23">
         <v>45657</v>
       </c>
       <c r="B385">
         <v>9.3535999999999699</v>
       </c>
-      <c r="C385" s="27">
+      <c r="C385" s="25">
         <f t="shared" si="11"/>
         <v>-1.6034034911438511E-4</v>
       </c>
@@ -15564,13 +15581,13 @@
       </c>
     </row>
     <row r="386" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A386" s="25">
+      <c r="A386" s="23">
         <v>45688</v>
       </c>
       <c r="B386">
         <v>9.4980999999999707</v>
       </c>
-      <c r="C386" s="27">
+      <c r="C386" s="25">
         <f t="shared" si="11"/>
         <v>1.5448597331508829E-2</v>
       </c>
@@ -15580,13 +15597,13 @@
       </c>
     </row>
     <row r="387" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A387" s="25">
+      <c r="A387" s="23">
         <v>45716</v>
       </c>
       <c r="B387">
         <v>9.5012999999999703</v>
       </c>
-      <c r="C387" s="27">
+      <c r="C387" s="25">
         <f t="shared" si="11"/>
         <v>3.36909487160586E-4</v>
       </c>
@@ -15596,13 +15613,13 @@
       </c>
     </row>
     <row r="388" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A388" s="25">
+      <c r="A388" s="23">
         <v>45747</v>
       </c>
       <c r="B388">
         <v>9.4220999999999702</v>
       </c>
-      <c r="C388" s="27">
+      <c r="C388" s="25">
         <f t="shared" si="11"/>
         <v>-8.3357014303305776E-3</v>
       </c>
@@ -15612,13 +15629,13 @@
       </c>
     </row>
     <row r="389" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A389" s="25">
+      <c r="A389" s="23">
         <v>45777</v>
       </c>
       <c r="B389">
         <v>9.3833999999999698</v>
       </c>
-      <c r="C389" s="27">
+      <c r="C389" s="25">
         <f t="shared" si="11"/>
         <v>-4.1073646002484088E-3</v>
       </c>
@@ -16171,7 +16188,7 @@
       <c r="I23" s="2"/>
       <c r="J23" s="2"/>
       <c r="K23" s="2"/>
-      <c r="L23" s="30" t="s">
+      <c r="L23" s="28" t="s">
         <v>7</v>
       </c>
       <c r="M23" s="2"/>
@@ -16193,7 +16210,7 @@
       <c r="I24" s="2"/>
       <c r="J24" s="2"/>
       <c r="K24" s="2"/>
-      <c r="L24" s="31" t="s">
+      <c r="L24" s="29" t="s">
         <v>8</v>
       </c>
       <c r="M24" s="2"/>
@@ -16215,7 +16232,7 @@
       <c r="I25" s="2"/>
       <c r="J25" s="2"/>
       <c r="K25" s="2"/>
-      <c r="L25" s="32" t="s">
+      <c r="L25" s="30" t="s">
         <v>3</v>
       </c>
       <c r="M25" s="2"/>
@@ -16237,7 +16254,7 @@
       <c r="I26" s="2"/>
       <c r="J26" s="2"/>
       <c r="K26" s="2"/>
-      <c r="L26" s="33" t="s">
+      <c r="L26" s="31" t="s">
         <v>4</v>
       </c>
       <c r="M26" s="2"/>
@@ -16259,7 +16276,7 @@
       <c r="I27" s="2"/>
       <c r="J27" s="2"/>
       <c r="K27" s="2"/>
-      <c r="L27" s="34" t="s">
+      <c r="L27" s="32" t="s">
         <v>9</v>
       </c>
       <c r="M27" s="2"/>
@@ -16345,22 +16362,22 @@
       <c r="A31" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B31" s="27">
+      <c r="B31" s="25">
         <v>1.47229339532977E-2</v>
       </c>
-      <c r="C31" s="27">
+      <c r="C31" s="25">
         <v>-2.2850820509186802E-3</v>
       </c>
-      <c r="D31" s="27">
+      <c r="D31" s="25">
         <v>4.4626087906761997E-3</v>
       </c>
-      <c r="E31" s="27">
+      <c r="E31" s="25">
         <v>2.562196973119E-3</v>
       </c>
-      <c r="F31" s="27">
+      <c r="F31" s="25">
         <v>-4.29657055318064E-4</v>
       </c>
-      <c r="G31" s="27">
+      <c r="G31" s="25">
         <v>1.6512662048122099E-3</v>
       </c>
       <c r="H31" s="5">
